--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87563억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 87836억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87134억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 87401억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 86401억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 86661억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85524억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 85778억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84762억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 84735억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 83550억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 83524억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 81993억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 81967억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -924,7 +924,7 @@
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 310억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 311억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
@@ -942,7 +942,7 @@
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 366억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 367억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1935,43 +1935,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87563억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87836억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87134억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87401억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 86401억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 86661억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85524억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85778억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84762억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 84735억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 83550억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 83524억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 81993억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 81967억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2408,7 +2408,7 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 310억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 311억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -2426,7 +2426,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 366억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 367억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6895,26 +6895,26 @@
         <v>0.063765</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.06796199999999999</v>
+        <v>-0.06504600000000001</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.08618000000000001</v>
+        <v>0.08949500000000001</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.016975</v>
+        <v>0.020079</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.018297</v>
+        <v>-0.015435</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.032021</v>
+        <v>-0.035315</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.041197</v>
+        <v>-0.044367</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.050984</v>
+        <v>-0.054196</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7044,29 +7044,29 @@
         <v>0.113871</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.113912</v>
+        <v>0.113924</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.113927</v>
+        <v>0.113919</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.113918</v>
+        <v>0.113895</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
+        <v>0.113891</v>
+      </c>
+      <c r="AL22" s="24" t="n">
         <v>0.113911</v>
       </c>
-      <c r="AL22" s="24" t="n">
-        <v>0.113878</v>
-      </c>
       <c r="AM22" s="24" t="n">
-        <v>0.113871</v>
+        <v>0.113902</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.113879</v>
+        <v>0.113918</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -7199,29 +7199,29 @@
         <v>0.178371</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178414</v>
+        <v>0.178408</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.17835</v>
+        <v>0.178399</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178346</v>
+        <v>0.178386</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.178363</v>
+        <v>0.178364</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178422</v>
+        <v>0.178378</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.17841</v>
+        <v>0.178369</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178347</v>
+        <v>0.178408</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7783,20 +7783,20 @@
         <v>0.049806</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.049875</v>
+        <v>0.050224</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.050092</v>
+        <v>0.049931</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.049929</v>
+        <v>0.050141</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.050056</v>
+        <v>0.049917</v>
       </c>
       <c r="AL27" s="24" t="n">
         <v>0.049847</v>
@@ -7805,7 +7805,7 @@
         <v>0.050189</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.049871</v>
+        <v>0.049889</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -8182,26 +8182,26 @@
         <v>0.10585</v>
       </c>
       <c r="AG30" s="24" t="n">
-        <v>-0.474294</v>
+        <v>-0.472846</v>
       </c>
       <c r="AH30" s="24" t="n">
-        <v>0.076711</v>
+        <v>0.079927</v>
       </c>
       <c r="AI30" s="24" t="n">
-        <v>0.015646</v>
+        <v>0.018707</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
       <c r="AK30" s="24" t="n">
-        <v>-0.016121</v>
+        <v>-0.013602</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>-0.028466</v>
+        <v>-0.031136</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>-0.036689</v>
+        <v>-0.039983</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>-0.046885</v>
+        <v>-0.050083</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8438,26 +8438,26 @@
         <v>0.01</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>-0.01</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL32" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AM32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AL32" s="29" t="n">
+      <c r="AN32" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AM32" s="29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AN32" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8566,26 +8566,26 @@
         <v>0.01</v>
       </c>
       <c r="AG33" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="29" t="n">
         <v>-0.01</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL33" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AM33" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AL33" s="29" t="n">
+      <c r="AN33" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AM33" s="29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AN33" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8822,26 +8822,26 @@
         <v>0.151398</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.145888</v>
+        <v>0.146347</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.138141</v>
+        <v>0.138486</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.157546</v>
+        <v>0.157904</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.086643</v>
+        <v>0.086809</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.087204</v>
+        <v>0.08705599999999999</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.086178</v>
+        <v>0.086046</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.101637</v>
+        <v>0.101544</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8950,26 +8950,26 @@
         <v>0.075726</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.07810300000000001</v>
+        <v>0.078349</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07860499999999999</v>
+        <v>0.078815</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.094595</v>
+        <v>0.094837</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.055015</v>
+        <v>0.055141</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.057031</v>
+        <v>0.056957</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.057969</v>
+        <v>0.057929</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.07019</v>
+        <v>0.070117</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9605,23 +9605,23 @@
         <v>-0.038251</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>0.254854</v>
+        <v>0.252427</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>0.046939</v>
+        <v>0.044898</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>0.077568</v>
+        <v>0.073375</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.022727</v>
+        <v>-0.024621</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>0.005803</v>
+        <v>0.005814</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.02729</v>
+        <v>0.029297</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -10025,29 +10025,29 @@
         <v>0.178371</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>0.178414</v>
+        <v>0.178408</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>0.17835</v>
+        <v>0.178399</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.178346</v>
+        <v>0.178386</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.178363</v>
+        <v>0.178364</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.178422</v>
+        <v>0.178378</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.17841</v>
+        <v>0.178369</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.178347</v>
+        <v>0.178408</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -31373,7 +31373,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>582.8</v>
+        <v>583.2</v>
       </c>
     </row>
     <row r="30">
@@ -31413,7 +31413,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1501</v>
+        <v>0.1502</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84957억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 85287억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87118억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 88687억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87836억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 92009억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87401억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 95873억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 86661억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 101010억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85778억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 107090억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84735억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 113604억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 83524억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 120051억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 81967억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 125764억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -912,37 +912,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 263억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 264억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 284억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 287억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 311억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 318억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 328억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 339억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 346억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 364억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 367억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 393억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1923,55 +1923,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84957억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85287억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87118억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88687억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87836억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 92009억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87401억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 95873억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 86661억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 101010억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85778억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 107090억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84735억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 113604억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 83524억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 120051억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 81967억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 125764억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2396,37 +2396,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 263억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 264억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 284억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 287억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 311억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 318억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 328억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 339억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 346억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 364억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 367억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 393억 × 1.09% − 총차입금 113억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4709,7 +4709,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 14.2, "op_wape_pct": 75.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 86.17, "rev_act": 115.07, "op_pred": 7.43, "op_act": 30.29}, {"q": "2025Q4", "rev_pred": 117.41, "rev_act": 130.35, "op_pred": 10.12, "op_act": 51.46}, {"q": "2026Q1", "rev_pred": 84.9, "rev_act": 91.97, "op_pred": 7.32, "op_act": 15.55}, {"q": "2026Q2", "rev_pred": 101.23, "rev_act": 116.6, "op_pred": 8.73, "op_act": 39.05}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 14.2, "op_wape_pct": 75.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 23.3, "wape_trend": 29.3, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 86.17, "rev_act": 115.07, "op_pred": 7.43, "op_act": 30.29}, {"q": "2025Q4", "rev_pred": 117.41, "rev_act": 130.35, "op_pred": 10.12, "op_act": 51.46}, {"q": "2026Q1", "rev_pred": 84.9, "rev_act": 91.97, "op_pred": 7.32, "op_act": 15.55}, {"q": "2026Q2", "rev_pred": 101.23, "rev_act": 116.6, "op_pred": 8.73, "op_act": 39.05}]}</t>
         </is>
       </c>
     </row>
@@ -6888,33 +6888,33 @@
         <v>-0.056112</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.161517</v>
+        <v>0.166043</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.063765</v>
+        <v>0.082903</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.06504600000000001</v>
+        <v>-0.020623</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.08949500000000001</v>
+        <v>0.195102</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.020079</v>
+        <v>0.184354</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.015435</v>
+        <v>0.207551</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.035315</v>
+        <v>0.234676</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.044367</v>
+        <v>0.252157</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.054196</v>
+        <v>0.245042</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7034,39 +7034,39 @@
         <v>0.113894</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.113871</v>
+        <v>0.113889</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.113871</v>
+        <v>0.113867</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.113924</v>
+        <v>0.113923</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.113919</v>
+        <v>0.113867</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.113895</v>
+        <v>0.113883</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.113891</v>
+        <v>0.11392</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.113911</v>
+        <v>0.113901</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.113902</v>
+        <v>0.113887</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.113918</v>
+        <v>0.113912</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -7189,23 +7189,23 @@
         <v>0.178345</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.178402</v>
+        <v>0.178367</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
+        <v>0.178331</v>
+      </c>
+      <c r="AG23" s="24" t="n">
         <v>0.178371</v>
       </c>
-      <c r="AG23" s="24" t="n">
-        <v>0.178408</v>
-      </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178399</v>
+        <v>0.178351</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178386</v>
+        <v>0.178379</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
@@ -7215,13 +7215,13 @@
         <v>0.178364</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178378</v>
+        <v>0.178369</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.178369</v>
+        <v>0.178367</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178408</v>
+        <v>0.178387</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7479,23 +7479,23 @@
         <v>0.72</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7773,39 +7773,39 @@
         <v>0.049824</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.050091</v>
+        <v>0.049892</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.049806</v>
+        <v>0.050054</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.050224</v>
+        <v>0.049905</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.049931</v>
+        <v>0.049832</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.050141</v>
+        <v>0.049863</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.049917</v>
+        <v>0.050179</v>
       </c>
       <c r="AL27" s="24" t="n">
         <v>0.049847</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.050189</v>
+        <v>0.050017</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.049889</v>
+        <v>0.049939</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -8175,33 +8175,33 @@
         <v>-0.334047</v>
       </c>
       <c r="AD30" s="24" t="n">
-        <v>-0.45414</v>
+        <v>-0.452098</v>
       </c>
       <c r="AE30" s="25" t="n"/>
       <c r="AF30" s="24" t="n">
-        <v>0.10585</v>
+        <v>0.12312</v>
       </c>
       <c r="AG30" s="24" t="n">
-        <v>-0.472846</v>
+        <v>-0.450398</v>
       </c>
       <c r="AH30" s="24" t="n">
-        <v>0.079927</v>
+        <v>0.173633</v>
       </c>
       <c r="AI30" s="24" t="n">
-        <v>0.018707</v>
+        <v>0.169434</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
       <c r="AK30" s="24" t="n">
-        <v>-0.013602</v>
+        <v>0.183036</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>-0.031136</v>
+        <v>0.209925</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>-0.039983</v>
+        <v>0.228571</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>-0.050083</v>
+        <v>0.22805</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8441,17 +8441,17 @@
         <v>0</v>
       </c>
       <c r="AH32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
@@ -8569,17 +8569,17 @@
         <v>0</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AL33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM33" s="29" t="n">
         <v>0</v>
@@ -8815,33 +8815,33 @@
         <v>0.276093</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.300126</v>
+        <v>0.301272</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.151398</v>
+        <v>0.153907</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.146347</v>
+        <v>0.152542</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.138486</v>
+        <v>0.150238</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.157904</v>
+        <v>0.17997</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.086809</v>
+        <v>0.103519</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.08705599999999999</v>
+        <v>0.109553</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.086046</v>
+        <v>0.113565</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.101544</v>
+        <v>0.139605</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8943,33 +8943,33 @@
         <v>0.103919</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.130478</v>
+        <v>0.130977</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.075726</v>
+        <v>0.077015</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.078349</v>
+        <v>0.08178100000000001</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.078815</v>
+        <v>0.085853</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.094837</v>
+        <v>0.108858</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.055141</v>
+        <v>0.066652</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.056957</v>
+        <v>0.073005</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.057929</v>
+        <v>0.078197</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.070117</v>
+        <v>0.099315</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9595,33 +9595,33 @@
         <v>-0.432507</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>-0.44</v>
+        <v>-0.441143</v>
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
-        <v>-0.414724</v>
+        <v>-0.417178</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.038251</v>
+        <v>-0.052823</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>0.252427</v>
+        <v>0.206311</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>0.044898</v>
+        <v>-0.038855</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>0.073375</v>
+        <v>-0.048421</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.024621</v>
+        <v>-0.173077</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>0.005814</v>
+        <v>-0.183099</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.029297</v>
+        <v>-0.193617</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9724,23 +9724,23 @@
         <v>-0.405172</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>-0.12987</v>
+        <v>-0.142857</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>-0.123288</v>
+        <v>-0.136986</v>
       </c>
       <c r="AJ43" s="25" t="n"/>
       <c r="AK43" s="24" t="n">
-        <v>-0.126761</v>
+        <v>-0.140845</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>-0.115942</v>
+        <v>-0.144928</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>-0.119403</v>
+        <v>-0.136364</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.109375</v>
+        <v>-0.142857</v>
       </c>
       <c r="AO43" s="25" t="n"/>
     </row>
@@ -10015,23 +10015,23 @@
         <v>0.178345</v>
       </c>
       <c r="AD45" s="24" t="n">
-        <v>0.178402</v>
+        <v>0.178367</v>
       </c>
       <c r="AE45" s="25">
         <f>IFERROR(subQ!AE36/subQ!AE35,"")</f>
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
+        <v>0.178331</v>
+      </c>
+      <c r="AG45" s="24" t="n">
         <v>0.178371</v>
       </c>
-      <c r="AG45" s="24" t="n">
-        <v>0.178408</v>
-      </c>
       <c r="AH45" s="24" t="n">
-        <v>0.178399</v>
+        <v>0.178351</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.178386</v>
+        <v>0.178379</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
@@ -10041,13 +10041,13 @@
         <v>0.178364</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.178378</v>
+        <v>0.178369</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.178369</v>
+        <v>0.178367</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.178408</v>
+        <v>0.178387</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31373,7 +31373,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>583.2</v>
+        <v>592.3</v>
       </c>
     </row>
     <row r="30">
@@ -31393,7 +31393,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.28</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="32">
@@ -31413,7 +31413,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1502</v>
+        <v>0.1525</v>
       </c>
     </row>
     <row r="34">
@@ -31423,7 +31423,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="35">
@@ -31433,7 +31433,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="36">
@@ -31443,7 +31443,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84766억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 84761억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87829억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 87818억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 90812억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 90794억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94520억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94496억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99648억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99624억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105726억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 105703억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 112240억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 112218억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 118689억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 118668억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 124404억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 124385억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84766억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 84761억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87829억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87818억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 90812억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 90794억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94520억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94496억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99648억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99624억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105726억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105703억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 112240억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 112218억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 118689억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 118668억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 124404억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 124385억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3080</v>
+        <v>3055</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3087.5</v>
+        <v>3076.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6561,33 +6561,33 @@
         <v>-0.058284507</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.158908389</v>
+        <v>0.158831671</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.072463894</v>
+        <v>0.072246422</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.033400883</v>
+        <v>-0.033572403</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180970838</v>
+        <v>0.180601698</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.17555938</v>
+        <v>0.175372393</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203690561</v>
+        <v>0.203731873</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.236003904</v>
+        <v>0.23595705</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255684926</v>
+        <v>0.255843039</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248451402</v>
+        <v>0.248507379</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6872,39 +6872,39 @@
         <v>0.178386859</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.178405931</v>
+        <v>0.178351539</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.178343303</v>
+        <v>0.178379475</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178333777</v>
+        <v>0.178365427</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178401188</v>
+        <v>0.178378801</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178398468</v>
+        <v>0.178382336</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.178402965</v>
+        <v>0.178348778</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178379154</v>
+        <v>0.178345778</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.17835584</v>
+        <v>0.178389145</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.17834912</v>
+        <v>0.178381305</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.002248475</v>
+        <v>-0.002325117</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.001624628</v>
+        <v>0.003717498</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.005543013</v>
+        <v>-0.004524956</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.013657666</v>
+        <v>-0.00373548</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.009137960000000001</v>
+        <v>0.001247773</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004156098</v>
+        <v>-0.002081986</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.001337366</v>
+        <v>-0.006544351</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.007487281</v>
+        <v>-0.000410861</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.006581835</v>
+        <v>0.00330293</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.005586426</v>
+        <v>-0.005745487</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.002248475</v>
+        <v>-0.002325117</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.001624628</v>
+        <v>0.003717498</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.005543013</v>
+        <v>-0.004524956</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.013657666</v>
+        <v>-0.00373548</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.009137960000000001</v>
+        <v>0.001247773</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.004156098</v>
+        <v>-0.002081986</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.001337366</v>
+        <v>-0.006544351</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.007487281</v>
+        <v>-0.000410861</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.006581835</v>
+        <v>0.00330293</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.005586426</v>
+        <v>-0.005745487</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8323,26 +8323,26 @@
         <v>0.140213124</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.139039187</v>
+        <v>0.138957206</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.137325464</v>
+        <v>0.137335349</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.164472852</v>
+        <v>0.164483261</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.096788218</v>
+        <v>0.09673913000000001</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.102417996</v>
+        <v>0.102428147</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.106341858</v>
+        <v>0.106306468</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.13057079</v>
+        <v>0.130586706</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8451,26 +8451,26 @@
         <v>0.0680374</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.072075135</v>
+        <v>0.072032638</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.07563325</v>
+        <v>0.075636248</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.095780357</v>
+        <v>0.095783887</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.05989776</v>
+        <v>0.059866142</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.065619546</v>
+        <v>0.065591978</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.07042253499999999</v>
+        <v>0.070428827</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.089434739</v>
+        <v>0.089414383</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>3080</v>
+        <v>3055</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2200197400888304</v>
+        <v>0.2200238575130599</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.113889026137655</v>
+        <v>0.1138879475883881</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001043058348425167</v>
+        <v>0.001043258331964601</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03626689891422773</v>
+        <v>0.0362672693137915</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31521,7 +31521,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>448</v>
+        <v>447.9</v>
       </c>
     </row>
     <row r="30">
@@ -31541,7 +31541,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.88</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="32">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1154</v>
+        <v>0.1153</v>
       </c>
     </row>
     <row r="34">
@@ -31591,7 +31591,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84761억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 84757억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87818억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 87806억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 90794억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 90775억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94496억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94470억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99624억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99596억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105703억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 105675억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 112218억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 112192억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 118668억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 118643억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 124385억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 124361억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84761억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 84757억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87818억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87806억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 90794억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 90775억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94496억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94470억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99624억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99596억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105703억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105675억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 112218억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 112192억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 118668억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 118643억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 124385억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 124361억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -6.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 4.1% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 22.01% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -6.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 4.1% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
     </row>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3055</v>
+        <v>2975</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6315,7 +6315,7 @@
         <v>2475</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3035</v>
+        <v>2950</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3076.7</v>
+        <v>3058.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6561,33 +6561,33 @@
         <v>-0.058284507</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.158831671</v>
+        <v>0.158754952</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.072246422</v>
+        <v>0.07213768600000001</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.033572403</v>
+        <v>-0.033829683</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180601698</v>
+        <v>0.180324843</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175372393</v>
+        <v>0.175119174</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203731873</v>
+        <v>0.203549696</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.23595705</v>
+        <v>0.236019883</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255843039</v>
+        <v>0.255824863</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248507379</v>
+        <v>0.248633726</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6872,39 +6872,39 @@
         <v>0.178386859</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.178351539</v>
+        <v>0.178363347</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.178379475</v>
+        <v>0.178397566</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178365427</v>
+        <v>0.178412924</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178378801</v>
+        <v>0.178342455</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178382336</v>
+        <v>0.178376247</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.178348778</v>
+        <v>0.178393865</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178345778</v>
+        <v>0.178384201</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.178389145</v>
+        <v>0.178371311</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178381305</v>
+        <v>0.178368378</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.002325117</v>
+        <v>-0.002990591</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.003717498</v>
+        <v>0.002776949</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.004524956</v>
+        <v>-0.005128296</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.00373548</v>
+        <v>0.005572839</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.001247773</v>
+        <v>-0.007341317</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.002081986</v>
+        <v>-0.0009928350000000001</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.006544351</v>
+        <v>0.00272304</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.000410861</v>
+        <v>-0.0012758</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.00330293</v>
+        <v>-0.005501194</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.005745487</v>
+        <v>-0.004942886</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.002325117</v>
+        <v>-0.002990591</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.003717498</v>
+        <v>0.002776949</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.004524956</v>
+        <v>-0.005128296</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.00373548</v>
+        <v>0.005572839</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.001247773</v>
+        <v>-0.007341317</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.002081986</v>
+        <v>-0.0009928350000000001</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.006544351</v>
+        <v>0.00272304</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.000410861</v>
+        <v>-0.0012758</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.00330293</v>
+        <v>-0.005501194</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.005745487</v>
+        <v>-0.004942886</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8320,29 +8320,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.140213124</v>
+        <v>0.140119649</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.138957206</v>
+        <v>0.139050586</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.137335349</v>
+        <v>0.13726337</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.164483261</v>
+        <v>0.16443038</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.09673913000000001</v>
+        <v>0.09674964699999999</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.102428147</v>
+        <v>0.10238874</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.106306468</v>
+        <v>0.106320806</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.130586706</v>
+        <v>0.13056199</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8444,33 +8444,33 @@
         <v>0.089938802</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.112558703</v>
+        <v>0.112508206</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.0680374</v>
+        <v>0.068085879</v>
       </c>
       <c r="AG34" s="24" t="n">
         <v>0.072032638</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.075636248</v>
+        <v>0.075596607</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.095783887</v>
+        <v>0.095750562</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.059866142</v>
+        <v>0.059870169</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.065591978</v>
+        <v>0.06556440600000001</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.070428827</v>
+        <v>0.070435119</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.089414383</v>
+        <v>0.089421846</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>3055</v>
+        <v>2975</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2200238575130599</v>
+        <v>0.2200600650018513</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1138879475883881</v>
+        <v>0.1138884769914067</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001043258331964601</v>
+        <v>0.001043463805126708</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0362672693137915</v>
+        <v>0.03626764339451787</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31521,7 +31521,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>447.9</v>
+        <v>447.8</v>
       </c>
     </row>
     <row r="30">
@@ -31541,7 +31541,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.82</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="32">
@@ -31551,7 +31551,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="33">
@@ -31591,7 +31591,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -663,43 +663,43 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84757억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 84754억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87806억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 87803억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 90775억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 90772억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94470억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94467억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99596억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99595억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105675억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 105674억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 112192억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 112191억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
@@ -1650,43 +1650,43 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84757억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 84754억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87806억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87803억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 90775억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 90772억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94470억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94467억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99596억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99595억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105675억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105674억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 112192억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 112191억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2975</v>
+        <v>2905</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6315,7 +6315,7 @@
         <v>2475</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2950</v>
+        <v>2870</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3058.8</v>
+        <v>3023</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6571,10 +6571,10 @@
         <v>-0.033829683</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180324843</v>
+        <v>0.180232558</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175119174</v>
+        <v>0.175052966</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
@@ -6584,10 +6584,10 @@
         <v>0.236019883</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255824863</v>
+        <v>0.255923059</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248633726</v>
+        <v>0.248704079</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6885,10 +6885,10 @@
         <v>0.178412924</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178342455</v>
+        <v>0.1783564</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178376247</v>
+        <v>0.178386297</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.002990591</v>
+        <v>-0.003156313</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.002776949</v>
+        <v>0.002542243</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.005128296</v>
+        <v>-0.005278464</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.005572839</v>
+        <v>0.005397835</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.007341317</v>
+        <v>-0.007538908</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.0009928350000000001</v>
+        <v>-0.001270727</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.00272304</v>
+        <v>0.002540064</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.0012758</v>
+        <v>-0.001492093</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.005501194</v>
+        <v>-0.005752084</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.004942886</v>
+        <v>-0.005292428</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.002990591</v>
+        <v>-0.003156313</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002776949</v>
+        <v>0.002542243</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.005128296</v>
+        <v>-0.005278464</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.005572839</v>
+        <v>0.005397835</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.007341317</v>
+        <v>-0.007538908</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.0009928350000000001</v>
+        <v>-0.001270727</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.00272304</v>
+        <v>0.002540064</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.0012758</v>
+        <v>-0.001492093</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.005501194</v>
+        <v>-0.005752084</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.004942886</v>
+        <v>-0.005292428</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8323,26 +8323,26 @@
         <v>0.140119649</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.139050586</v>
+        <v>0.138968599</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.13726337</v>
+        <v>0.137345235</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.16443038</v>
+        <v>0.164367089</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.09674964699999999</v>
+        <v>0.096754906</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.10238874</v>
+        <v>0.102443376</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.106320806</v>
+        <v>0.10627585</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.13056199</v>
+        <v>0.130607932</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8448,10 +8448,10 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.068085879</v>
+        <v>0.068040488</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.072032638</v>
+        <v>0.072078198</v>
       </c>
       <c r="AH34" s="24" t="n">
         <v>0.075596607</v>
@@ -8470,7 +8470,7 @@
         <v>0.070435119</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.089421846</v>
+        <v>0.089394024</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9133,11 +9133,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2975</v>
+        <v>2905</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,085원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,075원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2200600650018513</v>
+        <v>0.2200691187361145</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1138884769914067</v>
+        <v>0.113890085369901</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001043463805126708</v>
+        <v>0.001043449592365151</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03626764339451787</v>
+        <v>0.03626760062161501</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31541,7 +31541,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.64</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="32">
@@ -31551,7 +31551,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33">
@@ -31591,7 +31591,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -23,7 +23,7 @@
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
     <definedName name="BS연결">BS연결!$C$5:$AO$5</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
-    <definedName name="BS별도">BS별도!$C$5:$AO$95</definedName>
+    <definedName name="BS별도">BS별도!$C$5:$AO$98</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
     <definedName name="subQ">subQ!$A$5:$AO$42</definedName>
   </definedNames>
@@ -657,61 +657,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 80037억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 80223억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84754억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 85183억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87803억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 90772억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 91228억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94467억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94600억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99595억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99289억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105674억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 105070억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 112191억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 111421억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 118643억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 117844억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 124361억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 123670억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1644,61 +1644,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 80037억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 80223억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84754억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85183억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87803억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 90772억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91228억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94467억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94600억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99595억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99289억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105674억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105070억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 112191억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111421억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 118643억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117844억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 124361억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123670억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2022,25 +2022,25 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 235억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 236억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 252억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 253억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 271억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 272억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 297억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 298억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2082,25 +2082,25 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 235억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 252억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 253억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 271억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 272억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 297억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 298억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.01% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -6.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 4.1% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 21.99% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -6.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 4.1% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
     </row>
@@ -6558,36 +6558,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>-0.058284507</v>
+        <v>-0.056111852</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.158754952</v>
+        <v>0.164585552</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.07213768600000001</v>
+        <v>0.078226906</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.033829683</v>
+        <v>-0.028941372</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180232558</v>
+        <v>0.179173188</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175052966</v>
+        <v>0.165612648</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203549696</v>
+        <v>0.189895119</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.236019883</v>
+        <v>0.221319438</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255923059</v>
+        <v>0.245724994</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248704079</v>
+        <v>0.245563468</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6869,42 +6869,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.178386859</v>
+        <v>0.178344535</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.178363347</v>
+        <v>0.178392622</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.178397566</v>
+        <v>0.178398548</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178412924</v>
+        <v>0.178397951</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.1783564</v>
+        <v>0.178418053</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178386297</v>
+        <v>0.178365548</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.178393865</v>
+        <v>0.17840495</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178384201</v>
+        <v>0.178393232</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.178371311</v>
+        <v>0.178387865</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178368378</v>
+        <v>0.178365625</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003156313</v>
+        <v>0.000594952</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.002542243</v>
+        <v>0.00538313</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.005278464</v>
+        <v>-0.004933406</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.005397835</v>
+        <v>0.006114923</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.007538908</v>
+        <v>0.006772416</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.001270727</v>
+        <v>0.005085886</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.002540064</v>
+        <v>0.001805738</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.001492093</v>
+        <v>-0.000728797</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.005752084</v>
+        <v>0.009922965000000001</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.005292428</v>
+        <v>-0.001516197</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003156313</v>
+        <v>0.000594952</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002542243</v>
+        <v>0.00538313</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.005278464</v>
+        <v>-0.004933406</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.005397835</v>
+        <v>0.006114923</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.007538908</v>
+        <v>0.006772416</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.001270727</v>
+        <v>0.005085886</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.002540064</v>
+        <v>0.001805738</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.001492093</v>
+        <v>-0.000728797</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.005752084</v>
+        <v>0.009922965000000001</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.005292428</v>
+        <v>-0.001516197</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8313,36 +8313,36 @@
         <v/>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.239081237</v>
+        <v>0.239520108</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.263046045</v>
+        <v>0.264251151</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.140119649</v>
+        <v>0.140683346</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.138968599</v>
+        <v>0.139373107</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.137345235</v>
+        <v>0.137192932</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.164367089</v>
+        <v>0.163592724</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.096754906</v>
+        <v>0.09608077299999999</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.102443376</v>
+        <v>0.101723455</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.10627585</v>
+        <v>0.105592017</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.130607932</v>
+        <v>0.129945111</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8441,36 +8441,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.089938802</v>
+        <v>0.090158958</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.112508206</v>
+        <v>0.112990357</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.068040488</v>
+        <v>0.068360172</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.072078198</v>
+        <v>0.07230808399999999</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.075596607</v>
+        <v>0.075628588</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.095750562</v>
+        <v>0.09534327300000001</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.059870169</v>
+        <v>0.059519409</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.06556440600000001</v>
+        <v>0.06512085300000001</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.070435119</v>
+        <v>0.06995443599999999</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.089394024</v>
+        <v>0.08898352299999999</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2200691187361145</v>
+        <v>0.2199282976882185</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.113890085369901</v>
+        <v>0.1138951358538069</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001043449592365151</v>
+        <v>0.001044049219686043</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03626760062161501</v>
+        <v>0.03627019823816484</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10345,7 +10345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO95"/>
+  <dimension ref="A1:AO98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11114,55 +11114,55 @@
         <v>5444.25</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>5346.76</v>
+        <v>5681.06</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>4611.6</v>
+        <v>4984.28</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>5857.9</v>
+        <v>6039.03</v>
       </c>
       <c r="K7" s="37" t="n">
-        <v>5857.9</v>
+        <v>6039.03</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>4859.19</v>
+        <v>4979.35</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>4702.91</v>
+        <v>4813.76</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>4032.89</v>
+        <v>4126.7</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>6102.43</v>
+        <v>6262.42</v>
       </c>
       <c r="P7" s="37" t="n">
-        <v>6102.43</v>
+        <v>6262.42</v>
       </c>
       <c r="Q7" s="18" t="n">
-        <v>4252.74</v>
+        <v>4396.51</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>6380.87</v>
+        <v>6905.55</v>
       </c>
       <c r="S7" s="18" t="n">
-        <v>6224.25</v>
+        <v>6266.99</v>
       </c>
       <c r="T7" s="18" t="n">
-        <v>8404.27</v>
+        <v>8459.690000000001</v>
       </c>
       <c r="U7" s="37" t="n">
-        <v>8404.27</v>
+        <v>8459.690000000001</v>
       </c>
       <c r="V7" s="18" t="n">
-        <v>8198.59</v>
+        <v>8265.01</v>
       </c>
       <c r="W7" s="18" t="n">
-        <v>6911.11</v>
+        <v>6963.06</v>
       </c>
       <c r="X7" s="18" t="n">
-        <v>8124.96</v>
+        <v>8176.19</v>
       </c>
       <c r="Y7" s="18" t="n">
         <v>7277.09</v>
@@ -11208,9 +11208,57 @@
       <c r="G8" s="18" t="n">
         <v>436.36</v>
       </c>
-      <c r="K8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="U8" s="9" t="n"/>
+      <c r="H8" s="18" t="n">
+        <v>386.91</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>394.77</v>
+      </c>
+      <c r="K8" s="37" t="n">
+        <v>394.77</v>
+      </c>
+      <c r="L8" s="18" t="n">
+        <v>406.03</v>
+      </c>
+      <c r="M8" s="18" t="n">
+        <v>415.68</v>
+      </c>
+      <c r="N8" s="18" t="n">
+        <v>450.65</v>
+      </c>
+      <c r="O8" s="18" t="n">
+        <v>476.78</v>
+      </c>
+      <c r="P8" s="37" t="n">
+        <v>476.78</v>
+      </c>
+      <c r="Q8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U8" s="37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Z8" s="9" t="n"/>
       <c r="AB8" s="5" t="n"/>
       <c r="AC8" s="10" t="n"/>
@@ -11340,8 +11388,37 @@
       <c r="G10" s="18" t="n">
         <v>60.3</v>
       </c>
-      <c r="K10" s="9" t="n"/>
+      <c r="H10" s="18" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K10" s="37" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L10" s="18" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="N10" s="18" t="n">
+        <v>6.53</v>
+      </c>
       <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="R10" s="18" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="S10" s="18" t="n">
+        <v>12.18</v>
+      </c>
       <c r="U10" s="9" t="n"/>
       <c r="Z10" s="9" t="n"/>
       <c r="AB10" s="5" t="n"/>
@@ -11562,11 +11639,69 @@
       <c r="G13" s="18" t="n">
         <v>1.96</v>
       </c>
-      <c r="K13" s="9" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="U13" s="9" t="n"/>
-      <c r="Z13" s="9" t="n"/>
-      <c r="AB13" s="5" t="n"/>
+      <c r="H13" s="18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K13" s="37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L13" s="18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M13" s="18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N13" s="18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O13" s="18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P13" s="37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q13" s="18" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="R13" s="18" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="S13" s="18" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="T13" s="18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U13" s="37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V13" s="18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W13" s="18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X13" s="18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y13" s="18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z13" s="37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA13" s="18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB13" s="19" t="n">
+        <v>1.71</v>
+      </c>
       <c r="AC13" s="10" t="n"/>
       <c r="AD13" s="10" t="n"/>
       <c r="AE13" s="11" t="n"/>
@@ -11677,9 +11812,57 @@
       <c r="G15" s="18" t="n">
         <v>518.79</v>
       </c>
-      <c r="K15" s="9" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="U15" s="9" t="n"/>
+      <c r="H15" s="18" t="n">
+        <v>1037.18</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>1176.15</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>991.9299999999999</v>
+      </c>
+      <c r="K15" s="37" t="n">
+        <v>991.9299999999999</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <v>931.08</v>
+      </c>
+      <c r="M15" s="18" t="n">
+        <v>865.85</v>
+      </c>
+      <c r="N15" s="18" t="n">
+        <v>804.67</v>
+      </c>
+      <c r="O15" s="18" t="n">
+        <v>720.36</v>
+      </c>
+      <c r="P15" s="37" t="n">
+        <v>720.36</v>
+      </c>
+      <c r="Q15" s="18" t="n">
+        <v>838.4</v>
+      </c>
+      <c r="R15" s="18" t="n">
+        <v>1121.12</v>
+      </c>
+      <c r="S15" s="18" t="n">
+        <v>953.21</v>
+      </c>
+      <c r="T15" s="18" t="n">
+        <v>510.67</v>
+      </c>
+      <c r="U15" s="37" t="n">
+        <v>510.67</v>
+      </c>
+      <c r="V15" s="18" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="W15" s="18" t="n">
+        <v>511.92</v>
+      </c>
+      <c r="X15" s="18" t="n">
+        <v>530.15</v>
+      </c>
       <c r="Y15" s="18" t="n">
         <v>33.2</v>
       </c>
@@ -11724,9 +11907,57 @@
       <c r="G16" s="18" t="n">
         <v>518.79</v>
       </c>
-      <c r="K16" s="9" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="U16" s="9" t="n"/>
+      <c r="H16" s="18" t="n">
+        <v>1037.18</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>1176.15</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>991.9299999999999</v>
+      </c>
+      <c r="K16" s="37" t="n">
+        <v>991.9299999999999</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <v>931.08</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>865.85</v>
+      </c>
+      <c r="N16" s="18" t="n">
+        <v>804.67</v>
+      </c>
+      <c r="O16" s="18" t="n">
+        <v>720.36</v>
+      </c>
+      <c r="P16" s="37" t="n">
+        <v>720.36</v>
+      </c>
+      <c r="Q16" s="18" t="n">
+        <v>838.4</v>
+      </c>
+      <c r="R16" s="18" t="n">
+        <v>1121.12</v>
+      </c>
+      <c r="S16" s="18" t="n">
+        <v>953.21</v>
+      </c>
+      <c r="T16" s="18" t="n">
+        <v>510.67</v>
+      </c>
+      <c r="U16" s="37" t="n">
+        <v>510.67</v>
+      </c>
+      <c r="V16" s="18" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="W16" s="18" t="n">
+        <v>511.92</v>
+      </c>
+      <c r="X16" s="18" t="n">
+        <v>530.15</v>
+      </c>
       <c r="Y16" s="18" t="n">
         <v>33.2</v>
       </c>
@@ -12057,25 +12288,25 @@
         <v>4971.34</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>2204.35</v>
+        <v>2921.35</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>2463.55</v>
+        <v>3203.41</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>2797.5</v>
+        <v>3619.3</v>
       </c>
       <c r="K20" s="37" t="n">
-        <v>2797.5</v>
+        <v>3619.3</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>2490.2</v>
+        <v>3100.4</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>1891.23</v>
+        <v>2439.81</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>2085.78</v>
+        <v>2740.34</v>
       </c>
       <c r="O20" s="18" t="n">
         <v>1880.87</v>
@@ -12084,13 +12315,13 @@
         <v>1880.87</v>
       </c>
       <c r="Q20" s="18" t="n">
-        <v>1956.7</v>
+        <v>2441.5</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>2950.74</v>
+        <v>3560.44</v>
       </c>
       <c r="S20" s="18" t="n">
-        <v>2809.86</v>
+        <v>3458.49</v>
       </c>
       <c r="T20" s="18" t="n">
         <v>3832.84</v>
@@ -12151,11 +12382,69 @@
       <c r="G21" s="18" t="n">
         <v>17.89</v>
       </c>
-      <c r="K21" s="9" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="U21" s="9" t="n"/>
-      <c r="Z21" s="9" t="n"/>
-      <c r="AB21" s="5" t="n"/>
+      <c r="H21" s="18" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="K21" s="37" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="L21" s="18" t="n">
+        <v>272.7</v>
+      </c>
+      <c r="M21" s="18" t="n">
+        <v>173.76</v>
+      </c>
+      <c r="N21" s="18" t="n">
+        <v>73.20999999999999</v>
+      </c>
+      <c r="O21" s="18" t="n">
+        <v>372.04</v>
+      </c>
+      <c r="P21" s="37" t="n">
+        <v>372.04</v>
+      </c>
+      <c r="Q21" s="18" t="n">
+        <v>273.9</v>
+      </c>
+      <c r="R21" s="18" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="S21" s="18" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="T21" s="18" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="U21" s="37" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="V21" s="18" t="n">
+        <v>273.95</v>
+      </c>
+      <c r="W21" s="18" t="n">
+        <v>173.13</v>
+      </c>
+      <c r="X21" s="18" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="Y21" s="18" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="Z21" s="37" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="AA21" s="18" t="n">
+        <v>273.46</v>
+      </c>
+      <c r="AB21" s="19" t="n">
+        <v>172.94</v>
+      </c>
       <c r="AC21" s="10" t="n"/>
       <c r="AD21" s="10" t="n"/>
       <c r="AE21" s="11" t="n"/>
@@ -12188,11 +12477,69 @@
       <c r="G22" s="18" t="n">
         <v>17.89</v>
       </c>
-      <c r="K22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="U22" s="9" t="n"/>
-      <c r="Z22" s="9" t="n"/>
-      <c r="AB22" s="5" t="n"/>
+      <c r="H22" s="18" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>387.72</v>
+      </c>
+      <c r="K22" s="37" t="n">
+        <v>387.72</v>
+      </c>
+      <c r="L22" s="18" t="n">
+        <v>289.05</v>
+      </c>
+      <c r="M22" s="18" t="n">
+        <v>188.8</v>
+      </c>
+      <c r="N22" s="18" t="n">
+        <v>86.91</v>
+      </c>
+      <c r="O22" s="18" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="P22" s="37" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="Q22" s="18" t="n">
+        <v>284.89</v>
+      </c>
+      <c r="R22" s="18" t="n">
+        <v>184.01</v>
+      </c>
+      <c r="S22" s="18" t="n">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="T22" s="18" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="U22" s="37" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="V22" s="18" t="n">
+        <v>279.33</v>
+      </c>
+      <c r="W22" s="18" t="n">
+        <v>178.51</v>
+      </c>
+      <c r="X22" s="18" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="Y22" s="18" t="n">
+        <v>373.64</v>
+      </c>
+      <c r="Z22" s="37" t="n">
+        <v>373.64</v>
+      </c>
+      <c r="AA22" s="18" t="n">
+        <v>273.97</v>
+      </c>
+      <c r="AB22" s="19" t="n">
+        <v>172.94</v>
+      </c>
       <c r="AC22" s="10" t="n"/>
       <c r="AD22" s="10" t="n"/>
       <c r="AE22" s="11" t="n"/>
@@ -12225,11 +12572,69 @@
       <c r="G23" s="18" t="n">
         <v>17.89</v>
       </c>
-      <c r="K23" s="9" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="U23" s="9" t="n"/>
-      <c r="Z23" s="9" t="n"/>
-      <c r="AB23" s="5" t="n"/>
+      <c r="H23" s="18" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="K23" s="37" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="L23" s="18" t="n">
+        <v>272.7</v>
+      </c>
+      <c r="M23" s="18" t="n">
+        <v>173.76</v>
+      </c>
+      <c r="N23" s="18" t="n">
+        <v>73.20999999999999</v>
+      </c>
+      <c r="O23" s="18" t="n">
+        <v>372.04</v>
+      </c>
+      <c r="P23" s="37" t="n">
+        <v>372.04</v>
+      </c>
+      <c r="Q23" s="18" t="n">
+        <v>273.9</v>
+      </c>
+      <c r="R23" s="18" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="S23" s="18" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="T23" s="18" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="U23" s="37" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="V23" s="18" t="n">
+        <v>273.95</v>
+      </c>
+      <c r="W23" s="18" t="n">
+        <v>173.13</v>
+      </c>
+      <c r="X23" s="18" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="Y23" s="18" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="Z23" s="37" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="AA23" s="18" t="n">
+        <v>273.46</v>
+      </c>
+      <c r="AB23" s="19" t="n">
+        <v>172.94</v>
+      </c>
       <c r="AC23" s="10" t="n"/>
       <c r="AD23" s="10" t="n"/>
       <c r="AE23" s="11" t="n"/>
@@ -12262,11 +12667,69 @@
       <c r="G24" s="18" t="n">
         <v>175.44</v>
       </c>
-      <c r="K24" s="9" t="n"/>
-      <c r="P24" s="9" t="n"/>
-      <c r="U24" s="9" t="n"/>
-      <c r="Z24" s="9" t="n"/>
-      <c r="AB24" s="5" t="n"/>
+      <c r="H24" s="18" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>206.44</v>
+      </c>
+      <c r="K24" s="37" t="n">
+        <v>206.44</v>
+      </c>
+      <c r="L24" s="18" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>338.96</v>
+      </c>
+      <c r="N24" s="18" t="n">
+        <v>205.84</v>
+      </c>
+      <c r="O24" s="18" t="n">
+        <v>447.24</v>
+      </c>
+      <c r="P24" s="37" t="n">
+        <v>447.24</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>110.11</v>
+      </c>
+      <c r="R24" s="18" t="n">
+        <v>447.89</v>
+      </c>
+      <c r="S24" s="18" t="n">
+        <v>400.21</v>
+      </c>
+      <c r="T24" s="18" t="n">
+        <v>969.8099999999999</v>
+      </c>
+      <c r="U24" s="37" t="n">
+        <v>969.8099999999999</v>
+      </c>
+      <c r="V24" s="18" t="n">
+        <v>652.86</v>
+      </c>
+      <c r="W24" s="18" t="n">
+        <v>743.09</v>
+      </c>
+      <c r="X24" s="18" t="n">
+        <v>897.35</v>
+      </c>
+      <c r="Y24" s="18" t="n">
+        <v>998.78</v>
+      </c>
+      <c r="Z24" s="37" t="n">
+        <v>998.78</v>
+      </c>
+      <c r="AA24" s="18" t="n">
+        <v>672.61</v>
+      </c>
+      <c r="AB24" s="19" t="n">
+        <v>825.34</v>
+      </c>
       <c r="AC24" s="10" t="n"/>
       <c r="AD24" s="10" t="n"/>
       <c r="AE24" s="11" t="n"/>
@@ -13270,55 +13733,55 @@
         <v>5678.02</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>2153.23</v>
+        <v>3190.41</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>3257.79</v>
+        <v>4433.94</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>4263.21</v>
+        <v>5255.14</v>
       </c>
       <c r="K36" s="37" t="n">
-        <v>4263.21</v>
+        <v>5255.14</v>
       </c>
       <c r="L36" s="18" t="n">
-        <v>5807.43</v>
+        <v>6738.51</v>
       </c>
       <c r="M36" s="18" t="n">
-        <v>7324.53</v>
+        <v>8190.38</v>
       </c>
       <c r="N36" s="18" t="n">
-        <v>8502.74</v>
+        <v>9307.41</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>8819.120000000001</v>
+        <v>9539.48</v>
       </c>
       <c r="P36" s="37" t="n">
-        <v>8819.120000000001</v>
+        <v>9539.48</v>
       </c>
       <c r="Q36" s="18" t="n">
-        <v>12157.85</v>
+        <v>12996.25</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>2316.36</v>
+        <v>3437.48</v>
       </c>
       <c r="S36" s="18" t="n">
-        <v>2615.78</v>
+        <v>3568.99</v>
       </c>
       <c r="T36" s="18" t="n">
-        <v>4492.88</v>
+        <v>5003.55</v>
       </c>
       <c r="U36" s="37" t="n">
-        <v>4492.88</v>
+        <v>5003.55</v>
       </c>
       <c r="V36" s="18" t="n">
-        <v>3925.24</v>
+        <v>4436.74</v>
       </c>
       <c r="W36" s="18" t="n">
-        <v>4093.26</v>
+        <v>4605.18</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>5995.54</v>
+        <v>6525.69</v>
       </c>
       <c r="Y36" s="18" t="n">
         <v>13045.06</v>
@@ -13622,52 +14085,72 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>이연법인세자산</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
+      <c r="H40" s="18" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="K40" s="37" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="L40" s="18" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="N40" s="18" t="n">
+        <v>13.7</v>
+      </c>
       <c r="O40" s="18" t="n">
-        <v>211.18</v>
+        <v>12.36</v>
       </c>
       <c r="P40" s="37" t="n">
-        <v>211.18</v>
+        <v>12.36</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>211.18</v>
+        <v>10.99</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>182.61</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>238.74</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>1739.52</v>
+        <v>6.81</v>
       </c>
       <c r="U40" s="37" t="n">
-        <v>1739.52</v>
+        <v>6.81</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>1735.22</v>
+        <v>5.38</v>
       </c>
       <c r="W40" s="18" t="n">
-        <v>1742.46</v>
+        <v>5.38</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>1744.48</v>
+        <v>2.48</v>
       </c>
       <c r="Y40" s="18" t="n">
-        <v>1117.37</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>1117.37</v>
+        <v>1</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>1120.04</v>
+        <v>0.51</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>1101.47</v>
+        <v>0</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -13689,26 +14172,73 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
+      <c r="H41" s="18" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="K41" s="37" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="L41" s="18" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="N41" s="18" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="O41" s="18" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="P41" s="37" t="n">
+        <v>12.36</v>
+      </c>
       <c r="Q41" s="18" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="R41" s="18" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="S41" s="18" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="T41" s="18" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="U41" s="37" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="V41" s="18" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="W41" s="18" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="X41" s="18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="18" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB41" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R41" s="18" t="n">
-        <v>6600</v>
-      </c>
-      <c r="U41" s="9" t="n"/>
-      <c r="Y41" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="5" t="n"/>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
       <c r="AE41" s="11" t="n"/>
@@ -13729,47 +14259,52 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>장기차입금</t>
+          <t>이연법인세자산</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="K42" s="9" t="n"/>
-      <c r="P42" s="9" t="n"/>
+      <c r="O42" s="18" t="n">
+        <v>211.18</v>
+      </c>
+      <c r="P42" s="37" t="n">
+        <v>211.18</v>
+      </c>
       <c r="Q42" s="18" t="n">
-        <v>8000</v>
+        <v>211.18</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>8000</v>
+        <v>182.61</v>
       </c>
       <c r="S42" s="18" t="n">
-        <v>11300</v>
+        <v>238.74</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>11300</v>
+        <v>1739.52</v>
       </c>
       <c r="U42" s="37" t="n">
-        <v>11300</v>
+        <v>1739.52</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>11300</v>
+        <v>1735.22</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>11300</v>
+        <v>1742.46</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>11300</v>
+        <v>1744.48</v>
       </c>
       <c r="Y42" s="18" t="n">
-        <v>11300</v>
+        <v>1117.37</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>11300</v>
+        <v>1117.37</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>3300</v>
+        <v>1120.04</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>3300</v>
+        <v>1101.47</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -13791,17 +14326,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>단기금융부채(face)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
       <c r="K43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
-      <c r="S43" s="18" t="n">
-        <v>11300</v>
+      <c r="Q43" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="18" t="n">
+        <v>6600</v>
       </c>
       <c r="U43" s="9" t="n"/>
-      <c r="Z43" s="9" t="n"/>
+      <c r="Y43" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="AB43" s="5" t="n"/>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -13823,41 +14366,47 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>장기차입금</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="K44" s="9" t="n"/>
       <c r="P44" s="9" t="n"/>
+      <c r="Q44" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R44" s="18" t="n">
+        <v>8000</v>
+      </c>
       <c r="S44" s="18" t="n">
-        <v>-139.72</v>
+        <v>11300</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>-139.72</v>
+        <v>11300</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>-139.72</v>
+        <v>11300</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>-139.72</v>
+        <v>11300</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>-139.72</v>
+        <v>11300</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>-139.72</v>
+        <v>11300</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>-139.72</v>
+        <v>11300</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>-139.72</v>
+        <v>11300</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>-139.72</v>
+        <v>3300</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>-139.72</v>
+        <v>3300</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -13879,31 +14428,18 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>당기법인세부채(미지급법인세)</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="K45" s="9" t="n"/>
       <c r="P45" s="9" t="n"/>
+      <c r="S45" s="18" t="n">
+        <v>11300</v>
+      </c>
       <c r="U45" s="9" t="n"/>
-      <c r="W45" s="18" t="n">
-        <v>27.32</v>
-      </c>
-      <c r="X45" s="18" t="n">
-        <v>124.57</v>
-      </c>
-      <c r="Y45" s="18" t="n">
-        <v>340.6</v>
-      </c>
-      <c r="Z45" s="37" t="n">
-        <v>340.6</v>
-      </c>
-      <c r="AA45" s="18" t="n">
-        <v>250.2</v>
-      </c>
-      <c r="AB45" s="19" t="n">
-        <v>1188.36</v>
-      </c>
+      <c r="Z45" s="9" t="n"/>
+      <c r="AB45" s="5" t="n"/>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="11" t="n"/>
@@ -13924,24 +14460,41 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>단기금융상품</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
       <c r="K46" s="9" t="n"/>
       <c r="P46" s="9" t="n"/>
-      <c r="U46" s="9" t="n"/>
+      <c r="S46" s="18" t="n">
+        <v>-139.72</v>
+      </c>
+      <c r="T46" s="18" t="n">
+        <v>-139.72</v>
+      </c>
+      <c r="U46" s="37" t="n">
+        <v>-139.72</v>
+      </c>
+      <c r="V46" s="18" t="n">
+        <v>-139.72</v>
+      </c>
+      <c r="W46" s="18" t="n">
+        <v>-139.72</v>
+      </c>
+      <c r="X46" s="18" t="n">
+        <v>-139.72</v>
+      </c>
       <c r="Y46" s="18" t="n">
-        <v>0</v>
+        <v>-139.72</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>0</v>
+        <v>-139.72</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>1.18</v>
+        <v>-139.72</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>1.2</v>
+        <v>-139.72</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -13963,24 +14516,38 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>단기금융자산</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
       <c r="K47" s="9" t="n"/>
       <c r="P47" s="9" t="n"/>
-      <c r="U47" s="9" t="n"/>
+      <c r="T47" s="18" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="U47" s="37" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="V47" s="18" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="W47" s="18" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="X47" s="18" t="n">
+        <v>62.72</v>
+      </c>
       <c r="Y47" s="18" t="n">
-        <v>0</v>
+        <v>74.69</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>0</v>
+        <v>74.69</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>1.18</v>
+        <v>79.81</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>1.2</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -14002,24 +14569,30 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>사용권자산</t>
+          <t>당기법인세부채(미지급법인세)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
       <c r="K48" s="9" t="n"/>
       <c r="P48" s="9" t="n"/>
       <c r="U48" s="9" t="n"/>
+      <c r="W48" s="18" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="X48" s="18" t="n">
+        <v>124.57</v>
+      </c>
       <c r="Y48" s="18" t="n">
-        <v>372.51</v>
+        <v>340.6</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>372.51</v>
+        <v>340.6</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>271.35</v>
+        <v>250.2</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>170.19</v>
+        <v>1188.36</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -14041,7 +14614,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>기타비유동자산</t>
+          <t>단기금융상품</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -14049,16 +14622,16 @@
       <c r="P49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
       <c r="Y49" s="18" t="n">
-        <v>372.51</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>372.51</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>271.35</v>
+        <v>1.18</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>170.19</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -14080,19 +14653,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>유동성장기부채</t>
+          <t>단기금융자산</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
       <c r="K50" s="9" t="n"/>
       <c r="P50" s="9" t="n"/>
       <c r="U50" s="9" t="n"/>
-      <c r="Z50" s="9" t="n"/>
+      <c r="Y50" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="AA50" s="18" t="n">
-        <v>8000</v>
+        <v>1.18</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>8000</v>
+        <v>1.2</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -14114,78 +14692,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>8896.35</v>
+          <t>사용권자산</t>
+        </is>
       </c>
       <c r="F51" s="9" t="n"/>
-      <c r="G51" s="18" t="n">
-        <v>5724.77</v>
-      </c>
-      <c r="H51" s="18" t="n">
-        <v>6749.96</v>
-      </c>
-      <c r="I51" s="18" t="n">
-        <v>5989.29</v>
-      </c>
-      <c r="J51" s="18" t="n">
-        <v>6395.81</v>
-      </c>
-      <c r="K51" s="37" t="n">
-        <v>24859.83</v>
-      </c>
-      <c r="L51" s="18" t="n">
-        <v>6879.2</v>
-      </c>
-      <c r="M51" s="18" t="n">
-        <v>6790.69</v>
-      </c>
-      <c r="N51" s="18" t="n">
-        <v>5610.19</v>
-      </c>
-      <c r="O51" s="18" t="n">
-        <v>8027.89</v>
-      </c>
-      <c r="P51" s="37" t="n">
-        <v>27307.97</v>
-      </c>
-      <c r="Q51" s="18" t="n">
-        <v>5656.83</v>
-      </c>
-      <c r="R51" s="18" t="n">
-        <v>7734.21</v>
-      </c>
-      <c r="S51" s="18" t="n">
-        <v>9223.93</v>
-      </c>
-      <c r="T51" s="18" t="n">
-        <v>13101.01</v>
-      </c>
-      <c r="U51" s="37" t="n">
-        <v>35715.98</v>
-      </c>
-      <c r="V51" s="18" t="n">
-        <v>8468.74</v>
-      </c>
-      <c r="W51" s="18" t="n">
-        <v>8868.559999999999</v>
-      </c>
-      <c r="X51" s="18" t="n">
-        <v>11506.66</v>
-      </c>
+      <c r="K51" s="9" t="n"/>
+      <c r="P51" s="9" t="n"/>
+      <c r="U51" s="9" t="n"/>
       <c r="Y51" s="18" t="n">
-        <v>13034.68</v>
+        <v>372.51</v>
       </c>
       <c r="Z51" s="37" t="n">
-        <v>41878.64</v>
+        <v>372.51</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>9196.58</v>
+        <v>271.35</v>
       </c>
       <c r="AB51" s="19" t="n">
-        <v>11660.47</v>
+        <v>170.19</v>
       </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
@@ -14207,78 +14731,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>매출원가</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>7373.45</v>
+          <t>기타비유동자산</t>
+        </is>
       </c>
       <c r="F52" s="9" t="n"/>
-      <c r="G52" s="18" t="n">
-        <v>5385.2</v>
-      </c>
-      <c r="H52" s="18" t="n">
-        <v>5649.6</v>
-      </c>
-      <c r="I52" s="18" t="n">
-        <v>5301.5</v>
-      </c>
-      <c r="J52" s="18" t="n">
-        <v>4450.53</v>
-      </c>
-      <c r="K52" s="37" t="n">
-        <v>20786.83</v>
-      </c>
-      <c r="L52" s="18" t="n">
-        <v>5428.54</v>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>5771.85</v>
-      </c>
-      <c r="N52" s="18" t="n">
-        <v>4616.62</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>5047.97</v>
-      </c>
-      <c r="P52" s="37" t="n">
-        <v>20864.98</v>
-      </c>
-      <c r="Q52" s="18" t="n">
-        <v>4779.58</v>
-      </c>
-      <c r="R52" s="18" t="n">
-        <v>6116.21</v>
-      </c>
-      <c r="S52" s="18" t="n">
-        <v>6921.26</v>
-      </c>
-      <c r="T52" s="18" t="n">
-        <v>9113.049999999999</v>
-      </c>
-      <c r="U52" s="37" t="n">
-        <v>26930.1</v>
-      </c>
-      <c r="V52" s="18" t="n">
-        <v>6678.78</v>
-      </c>
-      <c r="W52" s="18" t="n">
-        <v>6892.84</v>
-      </c>
-      <c r="X52" s="18" t="n">
-        <v>7142.75</v>
-      </c>
+      <c r="K52" s="9" t="n"/>
+      <c r="P52" s="9" t="n"/>
+      <c r="U52" s="9" t="n"/>
       <c r="Y52" s="18" t="n">
-        <v>6432.4</v>
+        <v>372.51</v>
       </c>
       <c r="Z52" s="37" t="n">
-        <v>27146.77</v>
+        <v>372.51</v>
       </c>
       <c r="AA52" s="18" t="n">
-        <v>6303.8</v>
+        <v>271.35</v>
       </c>
       <c r="AB52" s="19" t="n">
-        <v>6608.51</v>
+        <v>170.19</v>
       </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
@@ -14300,78 +14770,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>매출총이익</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>1522.9</v>
+          <t>유동성장기부채</t>
+        </is>
       </c>
       <c r="F53" s="9" t="n"/>
-      <c r="G53" s="18" t="n">
-        <v>339.57</v>
-      </c>
-      <c r="H53" s="18" t="n">
-        <v>1100.36</v>
-      </c>
-      <c r="I53" s="18" t="n">
-        <v>687.79</v>
-      </c>
-      <c r="J53" s="18" t="n">
-        <v>1945.28</v>
-      </c>
-      <c r="K53" s="37" t="n">
-        <v>4073</v>
-      </c>
-      <c r="L53" s="18" t="n">
-        <v>1450.67</v>
-      </c>
-      <c r="M53" s="18" t="n">
-        <v>1018.84</v>
-      </c>
-      <c r="N53" s="18" t="n">
-        <v>993.5700000000001</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>2979.92</v>
-      </c>
-      <c r="P53" s="37" t="n">
-        <v>6443</v>
-      </c>
-      <c r="Q53" s="18" t="n">
-        <v>877.25</v>
-      </c>
-      <c r="R53" s="18" t="n">
-        <v>1618.01</v>
-      </c>
-      <c r="S53" s="18" t="n">
-        <v>2302.67</v>
-      </c>
-      <c r="T53" s="18" t="n">
-        <v>3987.95</v>
-      </c>
-      <c r="U53" s="37" t="n">
-        <v>8785.879999999999</v>
-      </c>
-      <c r="V53" s="18" t="n">
-        <v>1789.95</v>
-      </c>
-      <c r="W53" s="18" t="n">
-        <v>1975.72</v>
-      </c>
-      <c r="X53" s="18" t="n">
-        <v>4363.91</v>
-      </c>
-      <c r="Y53" s="18" t="n">
-        <v>6602.28</v>
-      </c>
-      <c r="Z53" s="37" t="n">
-        <v>14731.86</v>
-      </c>
+      <c r="K53" s="9" t="n"/>
+      <c r="P53" s="9" t="n"/>
+      <c r="U53" s="9" t="n"/>
+      <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="18" t="n">
-        <v>2892.78</v>
+        <v>8000</v>
       </c>
       <c r="AB53" s="19" t="n">
-        <v>5051.96</v>
+        <v>8000</v>
       </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
@@ -14393,78 +14804,78 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="E54" s="18" t="n">
-        <v>513.25</v>
+        <v>8896.35</v>
       </c>
       <c r="F54" s="9" t="n"/>
       <c r="G54" s="18" t="n">
-        <v>664.33</v>
+        <v>5724.77</v>
       </c>
       <c r="H54" s="18" t="n">
-        <v>547.6</v>
+        <v>6749.96</v>
       </c>
       <c r="I54" s="18" t="n">
-        <v>535.98</v>
+        <v>5989.29</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>925.95</v>
+        <v>6395.81</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>2673.86</v>
+        <v>24859.83</v>
       </c>
       <c r="L54" s="18" t="n">
-        <v>861.05</v>
+        <v>6879.2</v>
       </c>
       <c r="M54" s="18" t="n">
-        <v>671.89</v>
+        <v>6790.69</v>
       </c>
       <c r="N54" s="18" t="n">
-        <v>775.4400000000001</v>
+        <v>5610.19</v>
       </c>
       <c r="O54" s="18" t="n">
-        <v>720.46</v>
+        <v>8027.89</v>
       </c>
       <c r="P54" s="37" t="n">
-        <v>3028.84</v>
+        <v>27307.97</v>
       </c>
       <c r="Q54" s="18" t="n">
-        <v>955.45</v>
+        <v>5656.83</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>888.53</v>
+        <v>7734.21</v>
       </c>
       <c r="S54" s="18" t="n">
-        <v>1330.64</v>
+        <v>9223.93</v>
       </c>
       <c r="T54" s="18" t="n">
-        <v>1529.35</v>
+        <v>13101.01</v>
       </c>
       <c r="U54" s="37" t="n">
-        <v>4703.97</v>
+        <v>35715.98</v>
       </c>
       <c r="V54" s="18" t="n">
-        <v>1368.07</v>
+        <v>8468.74</v>
       </c>
       <c r="W54" s="18" t="n">
-        <v>1282.63</v>
+        <v>8868.559999999999</v>
       </c>
       <c r="X54" s="18" t="n">
-        <v>1335.39</v>
+        <v>11506.66</v>
       </c>
       <c r="Y54" s="18" t="n">
-        <v>1456.41</v>
+        <v>13034.68</v>
       </c>
       <c r="Z54" s="37" t="n">
-        <v>5442.5</v>
+        <v>41878.64</v>
       </c>
       <c r="AA54" s="18" t="n">
-        <v>1337.79</v>
+        <v>9196.58</v>
       </c>
       <c r="AB54" s="19" t="n">
-        <v>1147.2</v>
+        <v>11660.47</v>
       </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
@@ -14486,78 +14897,78 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E55" s="18" t="n">
-        <v>1009.65</v>
+        <v>7373.45</v>
       </c>
       <c r="F55" s="9" t="n"/>
       <c r="G55" s="18" t="n">
-        <v>-324.76</v>
+        <v>5385.2</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>552.76</v>
+        <v>5649.6</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>151.82</v>
+        <v>5301.5</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>1019.33</v>
+        <v>4450.53</v>
       </c>
       <c r="K55" s="37" t="n">
-        <v>1399.15</v>
+        <v>20786.83</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>589.62</v>
+        <v>5428.54</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>346.94</v>
+        <v>5771.85</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>218.14</v>
+        <v>4616.62</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>2259.46</v>
+        <v>5047.97</v>
       </c>
       <c r="P55" s="37" t="n">
-        <v>3414.16</v>
+        <v>20864.98</v>
       </c>
       <c r="Q55" s="18" t="n">
-        <v>-78.2</v>
+        <v>4779.58</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>729.48</v>
+        <v>6116.21</v>
       </c>
       <c r="S55" s="18" t="n">
-        <v>972.03</v>
+        <v>6921.26</v>
       </c>
       <c r="T55" s="18" t="n">
-        <v>2458.6</v>
+        <v>9113.049999999999</v>
       </c>
       <c r="U55" s="37" t="n">
-        <v>4081.91</v>
+        <v>26930.1</v>
       </c>
       <c r="V55" s="18" t="n">
-        <v>421.89</v>
+        <v>6678.78</v>
       </c>
       <c r="W55" s="18" t="n">
-        <v>693.09</v>
+        <v>6892.84</v>
       </c>
       <c r="X55" s="18" t="n">
-        <v>3028.52</v>
+        <v>7142.75</v>
       </c>
       <c r="Y55" s="18" t="n">
-        <v>5145.87</v>
+        <v>6432.4</v>
       </c>
       <c r="Z55" s="37" t="n">
-        <v>9289.370000000001</v>
+        <v>27146.77</v>
       </c>
       <c r="AA55" s="18" t="n">
-        <v>1554.99</v>
+        <v>6303.8</v>
       </c>
       <c r="AB55" s="19" t="n">
-        <v>3904.76</v>
+        <v>6608.51</v>
       </c>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
@@ -14579,78 +14990,78 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E56" s="18" t="n">
-        <v>311.96</v>
+        <v>1522.9</v>
       </c>
       <c r="F56" s="9" t="n"/>
       <c r="G56" s="18" t="n">
-        <v>64.19</v>
+        <v>339.57</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>43.86</v>
+        <v>1100.36</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>17.55</v>
+        <v>687.79</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>6.22</v>
+        <v>1945.28</v>
       </c>
       <c r="K56" s="37" t="n">
-        <v>131.82</v>
+        <v>4073</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>14.08</v>
+        <v>1450.67</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>18.05</v>
+        <v>1018.84</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>5.88</v>
+        <v>993.5700000000001</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>2.94</v>
+        <v>2979.92</v>
       </c>
       <c r="P56" s="37" t="n">
-        <v>40.95</v>
+        <v>6443</v>
       </c>
       <c r="Q56" s="18" t="n">
-        <v>10.4</v>
+        <v>877.25</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>12.07</v>
+        <v>1618.01</v>
       </c>
       <c r="S56" s="18" t="n">
-        <v>14.66</v>
+        <v>2302.67</v>
       </c>
       <c r="T56" s="18" t="n">
-        <v>35.14</v>
+        <v>3987.95</v>
       </c>
       <c r="U56" s="37" t="n">
-        <v>72.27</v>
+        <v>8785.879999999999</v>
       </c>
       <c r="V56" s="18" t="n">
-        <v>22.89</v>
+        <v>1789.95</v>
       </c>
       <c r="W56" s="18" t="n">
-        <v>45.86</v>
+        <v>1975.72</v>
       </c>
       <c r="X56" s="18" t="n">
-        <v>17.43</v>
+        <v>4363.91</v>
       </c>
       <c r="Y56" s="18" t="n">
-        <v>54.17</v>
+        <v>6602.28</v>
       </c>
       <c r="Z56" s="37" t="n">
-        <v>140.35</v>
+        <v>14731.86</v>
       </c>
       <c r="AA56" s="18" t="n">
-        <v>68.23</v>
+        <v>2892.78</v>
       </c>
       <c r="AB56" s="19" t="n">
-        <v>148.99</v>
+        <v>5051.96</v>
       </c>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
@@ -14672,78 +15083,78 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E57" s="18" t="n">
-        <v>4.17</v>
+        <v>513.25</v>
       </c>
       <c r="F57" s="9" t="n"/>
       <c r="G57" s="18" t="n">
-        <v>0.01</v>
+        <v>664.33</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>75.37</v>
+        <v>547.6</v>
       </c>
       <c r="I57" s="18" t="n">
-        <v>0.47</v>
+        <v>535.98</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>1.68</v>
+        <v>925.95</v>
       </c>
       <c r="K57" s="37" t="n">
-        <v>77.53</v>
+        <v>2673.86</v>
       </c>
       <c r="L57" s="18" t="n">
-        <v>4.18</v>
+        <v>861.05</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>11.72</v>
+        <v>671.89</v>
       </c>
       <c r="N57" s="18" t="n">
-        <v>-2.86</v>
+        <v>775.4400000000001</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>0.76</v>
+        <v>720.46</v>
       </c>
       <c r="P57" s="37" t="n">
-        <v>13.8</v>
+        <v>3028.84</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>1.84</v>
+        <v>955.45</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>0.45</v>
+        <v>888.53</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>2.23</v>
+        <v>1330.64</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>21.6</v>
+        <v>1529.35</v>
       </c>
       <c r="U57" s="37" t="n">
-        <v>26.12</v>
+        <v>4703.97</v>
       </c>
       <c r="V57" s="18" t="n">
-        <v>2.24</v>
+        <v>1368.07</v>
       </c>
       <c r="W57" s="18" t="n">
-        <v>0.33</v>
+        <v>1282.63</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>-0.37</v>
+        <v>1335.39</v>
       </c>
       <c r="Y57" s="18" t="n">
-        <v>1.34</v>
+        <v>1456.41</v>
       </c>
       <c r="Z57" s="37" t="n">
-        <v>3.54</v>
+        <v>5442.5</v>
       </c>
       <c r="AA57" s="18" t="n">
-        <v>20.27</v>
+        <v>1337.79</v>
       </c>
       <c r="AB57" s="19" t="n">
-        <v>42.38</v>
+        <v>1147.2</v>
       </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
@@ -14765,78 +15176,78 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E58" s="18" t="n">
-        <v>39.14</v>
+        <v>1009.65</v>
       </c>
       <c r="F58" s="9" t="n"/>
       <c r="G58" s="18" t="n">
-        <v>10.37</v>
+        <v>-324.76</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>34.33</v>
+        <v>552.76</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>190.06</v>
+        <v>151.82</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-174.05</v>
+        <v>1019.33</v>
       </c>
       <c r="K58" s="37" t="n">
-        <v>60.71</v>
+        <v>1399.15</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>17.91</v>
+        <v>589.62</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>70.88</v>
+        <v>346.94</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>44.8</v>
+        <v>218.14</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>38.77</v>
+        <v>2259.46</v>
       </c>
       <c r="P58" s="37" t="n">
-        <v>172.36</v>
+        <v>3414.16</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>178</v>
+        <v>-78.2</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>291.19</v>
+        <v>729.48</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>-5.1</v>
+        <v>972.03</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>444.83</v>
+        <v>2458.6</v>
       </c>
       <c r="U58" s="37" t="n">
-        <v>908.92</v>
+        <v>4081.91</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>11.5</v>
+        <v>421.89</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>17.88</v>
+        <v>693.09</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>24.31</v>
+        <v>3028.52</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>7.22</v>
+        <v>5145.87</v>
       </c>
       <c r="Z58" s="37" t="n">
-        <v>60.91</v>
+        <v>9289.370000000001</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>55.3</v>
+        <v>1554.99</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>7.89</v>
+        <v>3904.76</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -14858,78 +15269,78 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0.42</v>
+        <v>311.96</v>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="G59" s="18" t="n">
-        <v>43.28</v>
+        <v>64.19</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>125.16</v>
+        <v>43.86</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>81.48999999999999</v>
+        <v>17.55</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>54.72</v>
+        <v>6.22</v>
       </c>
       <c r="K59" s="37" t="n">
-        <v>304.65</v>
+        <v>131.82</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>157.29</v>
+        <v>14.08</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>188.97</v>
+        <v>18.05</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>171.54</v>
+        <v>5.88</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>191.49</v>
+        <v>2.94</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>709.29</v>
+        <v>40.95</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>98.04000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>113.67</v>
+        <v>12.07</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>185.5</v>
+        <v>14.66</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>150.6</v>
+        <v>35.14</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>547.8099999999999</v>
+        <v>72.27</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>138.61</v>
+        <v>22.89</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>282.02</v>
+        <v>45.86</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>43.9</v>
+        <v>17.43</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>109.55</v>
+        <v>54.17</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>574.08</v>
+        <v>140.35</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>113.27</v>
+        <v>68.23</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>111.7</v>
+        <v>148.99</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -14951,78 +15362,78 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>1356.17</v>
+        <v>4.17</v>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="G60" s="18" t="n">
-        <v>-293.49</v>
+        <v>0.01</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>430.42</v>
+        <v>75.37</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>277.46</v>
+        <v>0.47</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>795.1</v>
+        <v>1.68</v>
       </c>
       <c r="K60" s="37" t="n">
-        <v>1209.49</v>
+        <v>77.53</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>460.14</v>
+        <v>4.18</v>
       </c>
       <c r="M60" s="18" t="n">
-        <v>235.18</v>
+        <v>11.72</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>100.13</v>
+        <v>-2.86</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>2108.94</v>
+        <v>0.76</v>
       </c>
       <c r="P60" s="37" t="n">
-        <v>2904.39</v>
+        <v>13.8</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>10.32</v>
+        <v>1.84</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>918.62</v>
+        <v>0.45</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>793.87</v>
+        <v>2.23</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>2766.36</v>
+        <v>21.6</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>4489.17</v>
+        <v>26.12</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>315.42</v>
+        <v>2.24</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>474.47</v>
+        <v>0.33</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>3026.72</v>
+        <v>-0.37</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>5096.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>8912.98</v>
+        <v>3.54</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>1544.98</v>
+        <v>20.27</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>3907.57</v>
+        <v>42.38</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -15044,73 +15455,78 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>141.96</v>
+        <v>39.14</v>
       </c>
       <c r="F61" s="9" t="n"/>
+      <c r="G61" s="18" t="n">
+        <v>10.37</v>
+      </c>
       <c r="H61" s="18" t="n">
-        <v>1.46</v>
+        <v>34.33</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>85.34</v>
+        <v>190.06</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>-157.6</v>
-      </c>
-      <c r="K61" s="9" t="n"/>
+        <v>-174.05</v>
+      </c>
+      <c r="K61" s="37" t="n">
+        <v>60.71</v>
+      </c>
       <c r="L61" s="18" t="n">
-        <v>-4.54</v>
+        <v>17.91</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>33.88</v>
+        <v>70.88</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>-1.38</v>
+        <v>44.8</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>-1920.06</v>
+        <v>38.77</v>
       </c>
       <c r="P61" s="37" t="n">
-        <v>-1892.1</v>
+        <v>172.36</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>1.64</v>
+        <v>178</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>3.55</v>
+        <v>291.19</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>-54</v>
+        <v>-5.1</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>-1505.94</v>
+        <v>444.83</v>
       </c>
       <c r="U61" s="37" t="n">
-        <v>-1554.75</v>
+        <v>908.92</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>6.64</v>
+        <v>11.5</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>22.48</v>
+        <v>17.88</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>123.39</v>
+        <v>24.31</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>811.1799999999999</v>
+        <v>7.22</v>
       </c>
       <c r="Z61" s="37" t="n">
-        <v>963.6900000000001</v>
+        <v>60.91</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>63.31</v>
+        <v>55.3</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>1125.25</v>
+        <v>7.89</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -15132,78 +15548,78 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>1214.21</v>
+        <v>0.42</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="18" t="n">
-        <v>-293.49</v>
+        <v>43.28</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>428.95</v>
+        <v>125.16</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>192.13</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>952.7</v>
+        <v>54.72</v>
       </c>
       <c r="K62" s="37" t="n">
-        <v>1280.29</v>
+        <v>304.65</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>464.68</v>
+        <v>157.29</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>201.3</v>
+        <v>188.97</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>101.51</v>
+        <v>171.54</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>4029</v>
+        <v>191.49</v>
       </c>
       <c r="P62" s="37" t="n">
-        <v>4796.49</v>
+        <v>709.29</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>8.68</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>915.0700000000001</v>
+        <v>113.67</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>847.86</v>
+        <v>185.5</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>4272.29</v>
+        <v>150.6</v>
       </c>
       <c r="U62" s="37" t="n">
-        <v>6043.9</v>
+        <v>547.8099999999999</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>308.78</v>
+        <v>138.61</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>451.99</v>
+        <v>282.02</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>2903.33</v>
+        <v>43.9</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>4285.18</v>
+        <v>109.55</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>7949.28</v>
+        <v>574.08</v>
       </c>
       <c r="AA62" s="18" t="n">
-        <v>1481.66</v>
+        <v>113.27</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>2782.33</v>
+        <v>111.7</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -15225,78 +15641,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>1148.74</v>
+        <v>1356.17</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="18" t="n">
-        <v>-303.13</v>
+        <v>-293.49</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>694.58</v>
+        <v>430.42</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>186.11</v>
+        <v>277.46</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>1019.72</v>
+        <v>795.1</v>
       </c>
       <c r="K63" s="37" t="n">
-        <v>1597.28</v>
+        <v>1209.49</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>459.82</v>
+        <v>460.14</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>201.01</v>
+        <v>235.18</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>97.11</v>
+        <v>100.13</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>4032.88</v>
+        <v>2108.94</v>
       </c>
       <c r="P63" s="37" t="n">
-        <v>4790.82</v>
+        <v>2904.39</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>2.46</v>
+        <v>10.32</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>882.9</v>
+        <v>918.62</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>839.8</v>
+        <v>793.87</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>4291.78</v>
+        <v>2766.36</v>
       </c>
       <c r="U63" s="37" t="n">
-        <v>6016.94</v>
+        <v>4489.17</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>299.93</v>
+        <v>315.42</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>449.72</v>
+        <v>474.47</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>2895.69</v>
+        <v>3026.72</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>4359.27</v>
+        <v>5096.37</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>8004.61</v>
+        <v>8912.98</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>1472.19</v>
+        <v>1544.98</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>2848.16</v>
+        <v>3907.57</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -15318,78 +15734,73 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>38.72</v>
+        <v>141.96</v>
       </c>
       <c r="F64" s="9" t="n"/>
-      <c r="G64" s="18" t="n">
-        <v>-32.91</v>
-      </c>
       <c r="H64" s="18" t="n">
-        <v>-90.83</v>
+        <v>1.46</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>108.57</v>
+        <v>85.34</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-228.77</v>
-      </c>
-      <c r="K64" s="37" t="n">
-        <v>-243.94</v>
-      </c>
+        <v>-157.6</v>
+      </c>
+      <c r="K64" s="9" t="n"/>
       <c r="L64" s="18" t="n">
-        <v>-139.38</v>
+        <v>-4.54</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-118.09</v>
+        <v>33.88</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-126.74</v>
+        <v>-1.38</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>-152.72</v>
+        <v>-1920.06</v>
       </c>
       <c r="P64" s="37" t="n">
-        <v>-536.9299999999999</v>
+        <v>-1892.1</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>79.95999999999999</v>
+        <v>1.64</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>177.52</v>
+        <v>3.55</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>-190.6</v>
+        <v>-54</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>294.23</v>
+        <v>-1505.94</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>361.11</v>
+        <v>-1554.75</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>-127.11</v>
+        <v>6.64</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>-264.14</v>
+        <v>22.48</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>-19.59</v>
+        <v>123.39</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>-102.33</v>
+        <v>811.1799999999999</v>
       </c>
       <c r="Z64" s="37" t="n">
-        <v>-513.17</v>
+        <v>963.6900000000001</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>-57.97</v>
+        <v>63.31</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>-103.81</v>
+        <v>1125.25</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -15411,78 +15822,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>307.79</v>
+        <v>1214.21</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="18" t="n">
-        <v>64.18000000000001</v>
+        <v>-293.49</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>-31.51</v>
+        <v>428.95</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>17.08</v>
+        <v>192.13</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>4.54</v>
+        <v>952.7</v>
       </c>
       <c r="K65" s="37" t="n">
-        <v>54.29</v>
+        <v>1280.29</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>9.9</v>
+        <v>464.68</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>6.33</v>
+        <v>201.3</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>8.74</v>
+        <v>101.51</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>2.18</v>
+        <v>4029</v>
       </c>
       <c r="P65" s="37" t="n">
-        <v>27.15</v>
+        <v>4796.49</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>8.56</v>
+        <v>8.68</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>11.62</v>
+        <v>915.0700000000001</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>12.43</v>
+        <v>847.86</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>13.54</v>
+        <v>4272.29</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>46.15</v>
+        <v>6043.9</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>20.65</v>
+        <v>308.78</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>45.53</v>
+        <v>451.99</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>17.8</v>
+        <v>2903.33</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>52.83</v>
+        <v>4285.18</v>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>136.81</v>
+        <v>7949.28</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>47.96</v>
+        <v>1481.66</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>106.61</v>
+        <v>2782.33</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -15504,78 +15915,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>1214.21</v>
+        <v>1148.74</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="18" t="n">
-        <v>-293.49</v>
+        <v>-303.13</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>428.95</v>
+        <v>694.58</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>192.13</v>
+        <v>186.11</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>952.7</v>
+        <v>1019.72</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>1280.29</v>
+        <v>1597.28</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>464.68</v>
+        <v>459.82</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>201.3</v>
+        <v>201.01</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>101.51</v>
+        <v>97.11</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>4029</v>
+        <v>4032.88</v>
       </c>
       <c r="P66" s="37" t="n">
-        <v>4796.49</v>
+        <v>4790.82</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>8.68</v>
+        <v>2.46</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>915.0700000000001</v>
+        <v>882.9</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>847.86</v>
+        <v>839.8</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>4272.29</v>
+        <v>4291.78</v>
       </c>
       <c r="U66" s="37" t="n">
-        <v>6043.9</v>
+        <v>6016.94</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>308.78</v>
+        <v>299.93</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>451.99</v>
+        <v>449.72</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>2903.33</v>
+        <v>2895.69</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>4285.18</v>
+        <v>4359.27</v>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>7949.28</v>
+        <v>8004.61</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>1481.66</v>
+        <v>1472.19</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>2782.33</v>
+        <v>2848.16</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -15597,78 +16008,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>1214.21</v>
+        <v>38.72</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="18" t="n">
-        <v>-293.49</v>
+        <v>-32.91</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>428.95</v>
+        <v>-90.83</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>192.13</v>
+        <v>108.57</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>952.7</v>
+        <v>-228.77</v>
       </c>
       <c r="K67" s="37" t="n">
-        <v>1280.29</v>
+        <v>-243.94</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>464.68</v>
+        <v>-139.38</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>201.3</v>
+        <v>-118.09</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>101.51</v>
+        <v>-126.74</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>4029</v>
+        <v>-152.72</v>
       </c>
       <c r="P67" s="37" t="n">
-        <v>4796.49</v>
+        <v>-536.9299999999999</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>8.68</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>915.0700000000001</v>
+        <v>177.52</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>847.86</v>
+        <v>-190.6</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>4272.29</v>
+        <v>294.23</v>
       </c>
       <c r="U67" s="37" t="n">
-        <v>6043.9</v>
+        <v>361.11</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>308.78</v>
+        <v>-127.11</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>451.99</v>
+        <v>-264.14</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>2903.33</v>
+        <v>-19.59</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>4285.18</v>
+        <v>-102.33</v>
       </c>
       <c r="Z67" s="37" t="n">
-        <v>7949.28</v>
+        <v>-513.17</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>1481.66</v>
+        <v>-57.97</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>2782.33</v>
+        <v>-103.81</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -15690,70 +16101,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>이자수익</t>
-        </is>
+          <t>기타영업외손익</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>307.79</v>
       </c>
       <c r="F68" s="9" t="n"/>
+      <c r="G68" s="18" t="n">
+        <v>64.18000000000001</v>
+      </c>
       <c r="H68" s="18" t="n">
-        <v>0.01</v>
+        <v>-31.51</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>0.01</v>
+        <v>17.08</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="K68" s="9" t="n"/>
+        <v>4.54</v>
+      </c>
+      <c r="K68" s="37" t="n">
+        <v>54.29</v>
+      </c>
       <c r="L68" s="18" t="n">
-        <v>6.65</v>
+        <v>9.9</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>6.86</v>
+        <v>6.33</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>6.94</v>
+        <v>8.74</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>7.01</v>
+        <v>2.18</v>
       </c>
       <c r="P68" s="37" t="n">
-        <v>27.46</v>
+        <v>27.15</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>7.55</v>
+        <v>8.56</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>7.12</v>
+        <v>11.62</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>5.83</v>
+        <v>12.43</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>5.95</v>
+        <v>13.54</v>
       </c>
       <c r="U68" s="37" t="n">
-        <v>26.45</v>
+        <v>46.15</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>5.95</v>
+        <v>20.65</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>5.75</v>
+        <v>45.53</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>5.65</v>
+        <v>17.8</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>6.66</v>
+        <v>52.83</v>
       </c>
       <c r="Z68" s="37" t="n">
-        <v>24.01</v>
+        <v>136.81</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>0.33</v>
+        <v>47.96</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>0.97</v>
+        <v>106.61</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -15775,70 +16194,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
+          <t>(지배주주지분)당기순이익</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>1214.21</v>
       </c>
       <c r="F69" s="9" t="n"/>
+      <c r="G69" s="18" t="n">
+        <v>-293.49</v>
+      </c>
       <c r="H69" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>428.95</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>0.06</v>
+        <v>192.13</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>241.93</v>
-      </c>
-      <c r="K69" s="9" t="n"/>
+        <v>952.7</v>
+      </c>
+      <c r="K69" s="37" t="n">
+        <v>1280.29</v>
+      </c>
       <c r="L69" s="18" t="n">
-        <v>96.5</v>
+        <v>464.68</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>107.96</v>
+        <v>201.3</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>107.48</v>
+        <v>101.51</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>101.54</v>
+        <v>4029</v>
       </c>
       <c r="P69" s="37" t="n">
-        <v>413.48</v>
+        <v>4796.49</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>98.04000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>112.53</v>
+        <v>915.0700000000001</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>160.58</v>
+        <v>847.86</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>151</v>
+        <v>4272.29</v>
       </c>
       <c r="U69" s="37" t="n">
-        <v>522.15</v>
+        <v>6043.9</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>130.27</v>
+        <v>308.78</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>113.77</v>
+        <v>451.99</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>101.56</v>
+        <v>2903.33</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>98.92</v>
+        <v>4285.18</v>
       </c>
       <c r="Z69" s="37" t="n">
-        <v>444.52</v>
+        <v>7949.28</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>103.61</v>
+        <v>1481.66</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>105.5</v>
+        <v>2782.33</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -15860,70 +16287,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>이자손익</t>
-        </is>
+          <t>계속사업이익</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>1214.21</v>
       </c>
       <c r="F70" s="9" t="n"/>
+      <c r="G70" s="18" t="n">
+        <v>-293.49</v>
+      </c>
       <c r="H70" s="18" t="n">
-        <v>-0.06</v>
+        <v>428.95</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>-0.05</v>
+        <v>192.13</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>-206.89</v>
-      </c>
-      <c r="K70" s="9" t="n"/>
+        <v>952.7</v>
+      </c>
+      <c r="K70" s="37" t="n">
+        <v>1280.29</v>
+      </c>
       <c r="L70" s="18" t="n">
-        <v>-89.84999999999999</v>
+        <v>464.68</v>
       </c>
       <c r="M70" s="18" t="n">
-        <v>-101.1</v>
+        <v>201.3</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>-100.54</v>
+        <v>101.51</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>-94.53</v>
+        <v>4029</v>
       </c>
       <c r="P70" s="37" t="n">
-        <v>-386.02</v>
+        <v>4796.49</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>-90.48999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>-105.41</v>
+        <v>915.0700000000001</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>-154.75</v>
+        <v>847.86</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>-145.05</v>
+        <v>4272.29</v>
       </c>
       <c r="U70" s="37" t="n">
-        <v>-495.7</v>
+        <v>6043.9</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>-124.32</v>
+        <v>308.78</v>
       </c>
       <c r="W70" s="18" t="n">
-        <v>-108.02</v>
+        <v>451.99</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>-95.91</v>
+        <v>2903.33</v>
       </c>
       <c r="Y70" s="18" t="n">
-        <v>-92.26000000000001</v>
+        <v>4285.18</v>
       </c>
       <c r="Z70" s="37" t="n">
-        <v>-420.51</v>
+        <v>7949.28</v>
       </c>
       <c r="AA70" s="18" t="n">
-        <v>-103.28</v>
+        <v>1481.66</v>
       </c>
       <c r="AB70" s="19" t="n">
-        <v>-104.53</v>
+        <v>2782.33</v>
       </c>
       <c r="AC70" s="10" t="n"/>
       <c r="AD70" s="10" t="n"/>
@@ -15945,30 +16380,71 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>배당금수익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="F71" s="9" t="n"/>
+      <c r="H71" s="18" t="n">
+        <v>7.32</v>
+      </c>
       <c r="I71" s="18" t="n">
-        <v>0.03</v>
+        <v>7.07</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>31.33</v>
+        <v>10.3</v>
       </c>
       <c r="K71" s="9" t="n"/>
+      <c r="L71" s="18" t="n">
+        <v>6.65</v>
+      </c>
       <c r="M71" s="18" t="n">
-        <v>38.59</v>
+        <v>6.86</v>
       </c>
       <c r="N71" s="18" t="n">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="9" t="n"/>
-      <c r="U71" s="9" t="n"/>
-      <c r="Z71" s="9" t="n"/>
-      <c r="AB71" s="5" t="n"/>
+        <v>7.01</v>
+      </c>
+      <c r="P71" s="37" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="Q71" s="18" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="R71" s="18" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="S71" s="18" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="T71" s="18" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="U71" s="37" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="V71" s="18" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W71" s="18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X71" s="18" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Y71" s="18" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="Z71" s="37" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="AA71" s="18" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB71" s="19" t="n">
+        <v>0.97</v>
+      </c>
       <c r="AC71" s="10" t="n"/>
       <c r="AD71" s="10" t="n"/>
       <c r="AE71" s="11" t="n"/>
@@ -15989,42 +16465,70 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>외환차익</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="F72" s="9" t="n"/>
+      <c r="H72" s="18" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="I72" s="18" t="n">
+        <v>64.81</v>
+      </c>
+      <c r="J72" s="18" t="n">
+        <v>66.92</v>
+      </c>
       <c r="K72" s="9" t="n"/>
-      <c r="P72" s="9" t="n"/>
+      <c r="L72" s="18" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="M72" s="18" t="n">
+        <v>107.96</v>
+      </c>
+      <c r="N72" s="18" t="n">
+        <v>107.48</v>
+      </c>
+      <c r="O72" s="18" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="P72" s="37" t="n">
+        <v>413.48</v>
+      </c>
+      <c r="Q72" s="18" t="n">
+        <v>98.04000000000001</v>
+      </c>
       <c r="R72" s="18" t="n">
-        <v>0.11</v>
+        <v>112.53</v>
       </c>
       <c r="S72" s="18" t="n">
-        <v>1.02</v>
+        <v>160.58</v>
       </c>
       <c r="T72" s="18" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="U72" s="9" t="n"/>
+        <v>151</v>
+      </c>
+      <c r="U72" s="37" t="n">
+        <v>522.15</v>
+      </c>
       <c r="V72" s="18" t="n">
-        <v>3.27</v>
+        <v>130.27</v>
       </c>
       <c r="W72" s="18" t="n">
-        <v>2.94</v>
+        <v>113.77</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>2.21</v>
+        <v>101.56</v>
       </c>
       <c r="Y72" s="18" t="n">
-        <v>9.08</v>
+        <v>98.92</v>
       </c>
       <c r="Z72" s="37" t="n">
-        <v>17.5</v>
+        <v>444.52</v>
       </c>
       <c r="AA72" s="18" t="n">
-        <v>34.53</v>
+        <v>103.61</v>
       </c>
       <c r="AB72" s="19" t="n">
-        <v>13.38</v>
+        <v>105.5</v>
       </c>
       <c r="AC72" s="10" t="n"/>
       <c r="AD72" s="10" t="n"/>
@@ -16046,42 +16550,70 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="F73" s="9" t="n"/>
+      <c r="H73" s="18" t="n">
+        <v>-59.78</v>
+      </c>
+      <c r="I73" s="18" t="n">
+        <v>-57.74</v>
+      </c>
+      <c r="J73" s="18" t="n">
+        <v>-56.62</v>
+      </c>
       <c r="K73" s="9" t="n"/>
-      <c r="P73" s="9" t="n"/>
+      <c r="L73" s="18" t="n">
+        <v>-89.84999999999999</v>
+      </c>
+      <c r="M73" s="18" t="n">
+        <v>-101.1</v>
+      </c>
+      <c r="N73" s="18" t="n">
+        <v>-100.54</v>
+      </c>
+      <c r="O73" s="18" t="n">
+        <v>-94.53</v>
+      </c>
+      <c r="P73" s="37" t="n">
+        <v>-386.02</v>
+      </c>
+      <c r="Q73" s="18" t="n">
+        <v>-90.48999999999999</v>
+      </c>
       <c r="R73" s="18" t="n">
-        <v>0.1</v>
+        <v>-105.41</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>10.72</v>
+        <v>-154.75</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="U73" s="9" t="n"/>
+        <v>-145.05</v>
+      </c>
+      <c r="U73" s="37" t="n">
+        <v>-495.7</v>
+      </c>
       <c r="V73" s="18" t="n">
-        <v>3.1</v>
+        <v>-124.32</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>27.26</v>
+        <v>-108.02</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>86.8</v>
+        <v>-95.91</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>0.8</v>
+        <v>-92.26000000000001</v>
       </c>
       <c r="Z73" s="37" t="n">
-        <v>117.96</v>
+        <v>-420.51</v>
       </c>
       <c r="AA73" s="18" t="n">
-        <v>5.46</v>
+        <v>-103.28</v>
       </c>
       <c r="AB73" s="19" t="n">
-        <v>6.35</v>
+        <v>-104.53</v>
       </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
@@ -16103,43 +16635,30 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>외화환산이익</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="F74" s="9" t="n"/>
+      <c r="I74" s="18" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="J74" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K74" s="9" t="n"/>
+      <c r="M74" s="18" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="N74" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P74" s="9" t="n"/>
-      <c r="R74" s="18" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="S74" s="18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T74" s="18" t="n">
-        <v>92.65000000000001</v>
-      </c>
       <c r="U74" s="9" t="n"/>
-      <c r="V74" s="18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W74" s="18" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="X74" s="18" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="Y74" s="18" t="n">
-        <v>-3.89</v>
-      </c>
-      <c r="Z74" s="37" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA74" s="18" t="n">
-        <v>20.44</v>
-      </c>
-      <c r="AB74" s="19" t="n">
-        <v>-6.46</v>
-      </c>
+      <c r="Z74" s="9" t="n"/>
+      <c r="AB74" s="5" t="n"/>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
       <c r="AE74" s="11" t="n"/>
@@ -16160,42 +16679,42 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>외화환산손실</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="K75" s="9" t="n"/>
       <c r="P75" s="9" t="n"/>
       <c r="R75" s="18" t="n">
-        <v>1.03</v>
+        <v>0.11</v>
       </c>
       <c r="S75" s="18" t="n">
-        <v>14.2</v>
+        <v>1.02</v>
       </c>
       <c r="T75" s="18" t="n">
-        <v>-6.51</v>
+        <v>23.24</v>
       </c>
       <c r="U75" s="9" t="n"/>
       <c r="V75" s="18" t="n">
-        <v>5.24</v>
+        <v>3.27</v>
       </c>
       <c r="W75" s="18" t="n">
-        <v>140.98</v>
+        <v>2.94</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>-144.46</v>
+        <v>2.21</v>
       </c>
       <c r="Y75" s="18" t="n">
-        <v>9.82</v>
+        <v>9.08</v>
       </c>
       <c r="Z75" s="37" t="n">
-        <v>11.58</v>
+        <v>17.5</v>
       </c>
       <c r="AA75" s="18" t="n">
-        <v>4.2</v>
+        <v>34.53</v>
       </c>
       <c r="AB75" s="19" t="n">
-        <v>-0.15</v>
+        <v>13.38</v>
       </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
@@ -16217,78 +16736,42 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>90.41</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F76" s="9" t="n"/>
-      <c r="G76" s="18" t="n">
-        <v>-1301.67</v>
-      </c>
-      <c r="H76" s="18" t="n">
-        <v>-1328.31</v>
-      </c>
-      <c r="I76" s="18" t="n">
-        <v>1167.99</v>
-      </c>
-      <c r="J76" s="18" t="n">
-        <v>1066.35</v>
-      </c>
-      <c r="K76" s="37" t="n">
-        <v>-395.64</v>
-      </c>
-      <c r="L76" s="18" t="n">
-        <v>1625.83</v>
-      </c>
-      <c r="M76" s="18" t="n">
-        <v>1617.36</v>
-      </c>
-      <c r="N76" s="18" t="n">
-        <v>1289.98</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>544.49</v>
-      </c>
-      <c r="P76" s="37" t="n">
-        <v>5077.66</v>
-      </c>
-      <c r="Q76" s="18" t="n">
-        <v>2062.55</v>
-      </c>
+      <c r="K76" s="9" t="n"/>
+      <c r="P76" s="9" t="n"/>
       <c r="R76" s="18" t="n">
-        <v>-120.66</v>
+        <v>0.1</v>
       </c>
       <c r="S76" s="18" t="n">
-        <v>1179.42</v>
+        <v>10.72</v>
       </c>
       <c r="T76" s="18" t="n">
-        <v>1842.3</v>
-      </c>
-      <c r="U76" s="37" t="n">
-        <v>4963.61</v>
-      </c>
+        <v>6.12</v>
+      </c>
+      <c r="U76" s="9" t="n"/>
       <c r="V76" s="18" t="n">
-        <v>231.45</v>
+        <v>3.1</v>
       </c>
       <c r="W76" s="18" t="n">
-        <v>1341.84</v>
+        <v>27.26</v>
       </c>
       <c r="X76" s="18" t="n">
-        <v>1889.15</v>
+        <v>86.8</v>
       </c>
       <c r="Y76" s="18" t="n">
-        <v>6650.4</v>
+        <v>0.8</v>
       </c>
       <c r="Z76" s="37" t="n">
-        <v>10112.84</v>
+        <v>117.96</v>
       </c>
       <c r="AA76" s="18" t="n">
-        <v>2017.81</v>
+        <v>5.46</v>
       </c>
       <c r="AB76" s="19" t="n">
-        <v>3345.05</v>
+        <v>6.35</v>
       </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -16310,64 +16793,42 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>136.06</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F77" s="9" t="n"/>
-      <c r="G77" s="18" t="n">
-        <v>126.46</v>
-      </c>
-      <c r="H77" s="18" t="n">
-        <v>149.2</v>
-      </c>
-      <c r="I77" s="18" t="n">
-        <v>144.3</v>
-      </c>
-      <c r="J77" s="18" t="n">
-        <v>177.32</v>
-      </c>
-      <c r="K77" s="37" t="n">
-        <v>597.28</v>
-      </c>
-      <c r="L77" s="18" t="n">
-        <v>242.85</v>
-      </c>
-      <c r="M77" s="18" t="n">
-        <v>238.59</v>
-      </c>
-      <c r="N77" s="18" t="n">
-        <v>234.67</v>
-      </c>
-      <c r="O77" s="18" t="n">
-        <v>234.34</v>
-      </c>
-      <c r="P77" s="37" t="n">
-        <v>950.45</v>
+      <c r="K77" s="9" t="n"/>
+      <c r="P77" s="9" t="n"/>
+      <c r="R77" s="18" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="S77" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T77" s="18" t="n">
+        <v>92.65000000000001</v>
       </c>
       <c r="U77" s="9" t="n"/>
       <c r="V77" s="18" t="n">
-        <v>243.45</v>
+        <v>1.44</v>
       </c>
       <c r="W77" s="18" t="n">
-        <v>240.47</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>240.61</v>
+        <v>-1.78</v>
       </c>
       <c r="Y77" s="18" t="n">
-        <v>240.13</v>
+        <v>-3.89</v>
       </c>
       <c r="Z77" s="37" t="n">
-        <v>964.66</v>
+        <v>4.55</v>
       </c>
       <c r="AA77" s="18" t="n">
-        <v>239.67</v>
+        <v>20.44</v>
       </c>
       <c r="AB77" s="19" t="n">
-        <v>238.43</v>
+        <v>-6.46</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -16389,78 +16850,42 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>-5.9</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>-55.28</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="K78" s="37" t="n">
-        <v>-49.33</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>-3.39</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="P78" s="37" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>-1.1</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
       <c r="R78" s="18" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>-4.97</v>
+        <v>14.2</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>-61.46</v>
-      </c>
-      <c r="U78" s="37" t="n">
-        <v>-64.67</v>
-      </c>
+        <v>-6.51</v>
+      </c>
+      <c r="U78" s="9" t="n"/>
       <c r="V78" s="18" t="n">
-        <v>-0.92</v>
+        <v>5.24</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>67.73</v>
+        <v>140.98</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>-26.14</v>
+        <v>-144.46</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>-1.02</v>
+        <v>9.82</v>
       </c>
       <c r="Z78" s="37" t="n">
-        <v>39.65</v>
+        <v>11.58</v>
       </c>
       <c r="AA78" s="18" t="n">
-        <v>-153.72</v>
+        <v>4.2</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>-187.08</v>
+        <v>-0.15</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -16482,78 +16907,78 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>2100.72</v>
+        <v>90.41</v>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="18" t="n">
-        <v>-5327.88</v>
+        <v>-1301.67</v>
       </c>
       <c r="H79" s="18" t="n">
-        <v>-1712.8</v>
+        <v>-1328.31</v>
       </c>
       <c r="I79" s="18" t="n">
-        <v>-62.86</v>
+        <v>1167.99</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>-27.58</v>
+        <v>1066.35</v>
       </c>
       <c r="K79" s="37" t="n">
-        <v>-7131.12</v>
+        <v>-395.64</v>
       </c>
       <c r="L79" s="18" t="n">
-        <v>17.05</v>
+        <v>1625.83</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0</v>
+        <v>1617.36</v>
       </c>
       <c r="N79" s="18" t="n">
-        <v>-9.890000000000001</v>
+        <v>1289.98</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>-126.42</v>
+        <v>544.49</v>
       </c>
       <c r="P79" s="37" t="n">
-        <v>-119.26</v>
+        <v>5077.66</v>
       </c>
       <c r="Q79" s="18" t="n">
-        <v>506.12</v>
+        <v>2062.55</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>-12620.07</v>
+        <v>-120.66</v>
       </c>
       <c r="S79" s="18" t="n">
-        <v>70.42</v>
+        <v>1179.42</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>761.27</v>
+        <v>1842.3</v>
       </c>
       <c r="U79" s="37" t="n">
-        <v>-11282.26</v>
+        <v>4963.61</v>
       </c>
       <c r="V79" s="18" t="n">
-        <v>-117.22</v>
+        <v>231.45</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>-12.44</v>
+        <v>1341.84</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>-29.35</v>
+        <v>1889.15</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>474.17</v>
+        <v>6650.4</v>
       </c>
       <c r="Z79" s="37" t="n">
-        <v>315.16</v>
+        <v>10112.84</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>-49.15</v>
+        <v>2017.81</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>5</v>
+        <v>3345.05</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -16575,30 +17000,65 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E80" s="18" t="n">
-        <v>46.29</v>
+        <v>136.06</v>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="18" t="n">
-        <v>41.79</v>
-      </c>
-      <c r="K80" s="9" t="n"/>
-      <c r="P80" s="9" t="n"/>
-      <c r="Q80" s="18" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="R80" s="18" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="S80" s="18" t="n">
-        <v>5.83</v>
+        <v>126.46</v>
+      </c>
+      <c r="H80" s="18" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="I80" s="18" t="n">
+        <v>144.3</v>
+      </c>
+      <c r="J80" s="18" t="n">
+        <v>177.32</v>
+      </c>
+      <c r="K80" s="37" t="n">
+        <v>597.28</v>
+      </c>
+      <c r="L80" s="18" t="n">
+        <v>242.85</v>
+      </c>
+      <c r="M80" s="18" t="n">
+        <v>238.59</v>
+      </c>
+      <c r="N80" s="18" t="n">
+        <v>234.67</v>
+      </c>
+      <c r="O80" s="18" t="n">
+        <v>234.34</v>
+      </c>
+      <c r="P80" s="37" t="n">
+        <v>950.45</v>
       </c>
       <c r="U80" s="9" t="n"/>
-      <c r="Z80" s="9" t="n"/>
-      <c r="AB80" s="5" t="n"/>
+      <c r="V80" s="18" t="n">
+        <v>243.45</v>
+      </c>
+      <c r="W80" s="18" t="n">
+        <v>240.47</v>
+      </c>
+      <c r="X80" s="18" t="n">
+        <v>240.61</v>
+      </c>
+      <c r="Y80" s="18" t="n">
+        <v>240.13</v>
+      </c>
+      <c r="Z80" s="37" t="n">
+        <v>964.66</v>
+      </c>
+      <c r="AA80" s="18" t="n">
+        <v>239.67</v>
+      </c>
+      <c r="AB80" s="19" t="n">
+        <v>238.43</v>
+      </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
       <c r="AE80" s="11" t="n"/>
@@ -16619,36 +17079,79 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0</v>
+        <v>-5.9</v>
       </c>
       <c r="F81" s="9" t="n"/>
+      <c r="G81" s="18" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H81" s="18" t="n">
+        <v>1.05</v>
+      </c>
       <c r="I81" s="18" t="n">
-        <v>31.36</v>
+        <v>-55.28</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="9" t="n"/>
+        <v>-7.8</v>
+      </c>
+      <c r="K81" s="37" t="n">
+        <v>-49.33</v>
+      </c>
+      <c r="L81" s="18" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="M81" s="18" t="n">
+        <v>9.02</v>
+      </c>
       <c r="N81" s="18" t="n">
-        <v>0</v>
+        <v>-3.39</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="9" t="n"/>
+        <v>-1.1</v>
+      </c>
+      <c r="P81" s="37" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q81" s="18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="R81" s="18" t="n">
+        <v>2.86</v>
+      </c>
       <c r="S81" s="18" t="n">
-        <v>0</v>
+        <v>-4.97</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" s="9" t="n"/>
-      <c r="Z81" s="9" t="n"/>
-      <c r="AB81" s="5" t="n"/>
+        <v>-61.46</v>
+      </c>
+      <c r="U81" s="37" t="n">
+        <v>-64.67</v>
+      </c>
+      <c r="V81" s="18" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="W81" s="18" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="X81" s="18" t="n">
+        <v>-26.14</v>
+      </c>
+      <c r="Y81" s="18" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="Z81" s="37" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="AA81" s="18" t="n">
+        <v>-153.72</v>
+      </c>
+      <c r="AB81" s="19" t="n">
+        <v>-187.08</v>
+      </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -16669,78 +17172,78 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>-31.74</v>
+        <v>2100.72</v>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="18" t="n">
-        <v>7932.9</v>
+        <v>-5327.88</v>
       </c>
       <c r="H82" s="18" t="n">
-        <v>35.11</v>
+        <v>-1712.8</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>-0.57</v>
+        <v>-62.86</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>-33.36</v>
+        <v>-27.58</v>
       </c>
       <c r="K82" s="37" t="n">
-        <v>7934.08</v>
+        <v>-7131.12</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>-98.66</v>
+        <v>17.05</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>-100.26</v>
+        <v>0</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>-101.88</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>-101.7</v>
+        <v>-126.42</v>
       </c>
       <c r="P82" s="37" t="n">
-        <v>-402.5</v>
+        <v>-119.26</v>
       </c>
       <c r="Q82" s="18" t="n">
-        <v>770.0599999999999</v>
+        <v>506.12</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>2899.13</v>
+        <v>-12620.07</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>-941.98</v>
+        <v>70.42</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>-814.79</v>
+        <v>761.27</v>
       </c>
       <c r="U82" s="37" t="n">
-        <v>1912.42</v>
+        <v>-11282.26</v>
       </c>
       <c r="V82" s="18" t="n">
-        <v>-682.73</v>
+        <v>-117.22</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>-1017.51</v>
+        <v>-12.44</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>-102.25</v>
+        <v>-29.35</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>-101.9</v>
+        <v>474.17</v>
       </c>
       <c r="Z82" s="37" t="n">
-        <v>-1904.39</v>
+        <v>315.16</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>-99.68000000000001</v>
+        <v>-49.15</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>-101.03</v>
+        <v>5</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -16762,18 +17265,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>-0.66</v>
+        <v>46.29</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>-43.28</v>
+        <v>41.79</v>
       </c>
       <c r="K83" s="9" t="n"/>
       <c r="P83" s="9" t="n"/>
+      <c r="Q83" s="18" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="R83" s="18" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="S83" s="18" t="n">
+        <v>5.83</v>
+      </c>
       <c r="U83" s="9" t="n"/>
       <c r="Z83" s="9" t="n"/>
       <c r="AB83" s="5" t="n"/>
@@ -16797,79 +17309,36 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>31.09</v>
+        <v>0</v>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="18" t="n">
-        <v>23.82</v>
-      </c>
-      <c r="H84" s="18" t="n">
-        <v>8.17</v>
-      </c>
       <c r="I84" s="18" t="n">
-        <v>0.57</v>
+        <v>31.36</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>33.36</v>
-      </c>
-      <c r="K84" s="37" t="n">
-        <v>65.92</v>
-      </c>
-      <c r="L84" s="18" t="n">
-        <v>98.66</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>100.26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K84" s="9" t="n"/>
       <c r="N84" s="18" t="n">
-        <v>101.88</v>
+        <v>0</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="P84" s="37" t="n">
-        <v>402.5</v>
-      </c>
-      <c r="Q84" s="18" t="n">
-        <v>99.51000000000001</v>
-      </c>
-      <c r="R84" s="18" t="n">
-        <v>100.87</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P84" s="9" t="n"/>
       <c r="S84" s="18" t="n">
-        <v>102.26</v>
+        <v>0</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>101.78</v>
-      </c>
-      <c r="U84" s="37" t="n">
-        <v>404.42</v>
-      </c>
-      <c r="V84" s="18" t="n">
-        <v>99.41</v>
-      </c>
-      <c r="W84" s="18" t="n">
-        <v>100.83</v>
-      </c>
-      <c r="X84" s="18" t="n">
-        <v>102.25</v>
-      </c>
-      <c r="Y84" s="18" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="Z84" s="37" t="n">
-        <v>404.39</v>
-      </c>
-      <c r="AA84" s="18" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="AB84" s="19" t="n">
-        <v>101.03</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U84" s="9" t="n"/>
+      <c r="Z84" s="9" t="n"/>
+      <c r="AB84" s="5" t="n"/>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
       <c r="AE84" s="11" t="n"/>
@@ -16890,78 +17359,78 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>2159.38</v>
+        <v>-31.74</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>1303.35</v>
+        <v>7932.9</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>-3006</v>
+        <v>35.11</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>1104.56</v>
+        <v>-0.57</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>1005.41</v>
+        <v>-33.36</v>
       </c>
       <c r="K85" s="37" t="n">
-        <v>407.32</v>
+        <v>7934.08</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>1544.22</v>
+        <v>-98.66</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>1517.11</v>
+        <v>-100.26</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>1178.2</v>
+        <v>-101.88</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>316.38</v>
+        <v>-101.7</v>
       </c>
       <c r="P85" s="37" t="n">
-        <v>4555.91</v>
+        <v>-402.5</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>3338.73</v>
+        <v>770.0599999999999</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>-9841.49</v>
+        <v>2899.13</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>299.42</v>
+        <v>-941.98</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>1877.1</v>
+        <v>-814.79</v>
       </c>
       <c r="U85" s="37" t="n">
-        <v>-4326.24</v>
+        <v>1912.42</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>-567.64</v>
+        <v>-682.73</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>168.02</v>
+        <v>-1017.51</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>1902.28</v>
+        <v>-102.25</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>7016.32</v>
+        <v>-101.9</v>
       </c>
       <c r="Z85" s="37" t="n">
-        <v>8518.98</v>
+        <v>-1904.39</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>1878.18</v>
+        <v>-99.68000000000001</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>3244.46</v>
+        <v>-101.03</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -16983,79 +17452,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>2159.37</v>
+        <v>-0.66</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>5159.23</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>-3006</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>1104.56</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>1005.42</v>
-      </c>
-      <c r="K86" s="37" t="n">
-        <v>4263.21</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>5807.43</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>1517.1</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>1178.21</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>316.38</v>
-      </c>
-      <c r="P86" s="37" t="n">
-        <v>8819.120000000001</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>12157.85</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>-9841.49</v>
-      </c>
-      <c r="S86" s="18" t="n">
-        <v>299.42</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>1877.1</v>
-      </c>
-      <c r="U86" s="37" t="n">
-        <v>4492.88</v>
-      </c>
-      <c r="V86" s="18" t="n">
-        <v>3925.24</v>
-      </c>
-      <c r="W86" s="18" t="n">
-        <v>168.02</v>
-      </c>
-      <c r="X86" s="18" t="n">
-        <v>1902.28</v>
-      </c>
-      <c r="Y86" s="18" t="n">
-        <v>7016.32</v>
-      </c>
-      <c r="Z86" s="37" t="n">
-        <v>13011.86</v>
-      </c>
-      <c r="AA86" s="18" t="n">
-        <v>14890.05</v>
-      </c>
-      <c r="AB86" s="19" t="n">
-        <v>3244.46</v>
-      </c>
+        <v>-43.28</v>
+      </c>
+      <c r="K86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
+      <c r="Z86" s="9" t="n"/>
+      <c r="AB86" s="5" t="n"/>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
       <c r="AE86" s="11" t="n"/>
@@ -17076,47 +17487,79 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>31.09</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>8000</v>
+        <v>23.82</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>0</v>
+        <v>8.17</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>2400</v>
+        <v>33.36</v>
       </c>
       <c r="K87" s="37" t="n">
-        <v>10400</v>
+        <v>65.92</v>
+      </c>
+      <c r="L87" s="18" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="M87" s="18" t="n">
+        <v>100.26</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>0</v>
+        <v>101.88</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="9" t="n"/>
+        <v>101.7</v>
+      </c>
+      <c r="P87" s="37" t="n">
+        <v>402.5</v>
+      </c>
+      <c r="Q87" s="18" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="R87" s="18" t="n">
+        <v>100.87</v>
+      </c>
       <c r="S87" s="18" t="n">
-        <v>0</v>
+        <v>102.26</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" s="9" t="n"/>
+        <v>101.78</v>
+      </c>
+      <c r="U87" s="37" t="n">
+        <v>404.42</v>
+      </c>
+      <c r="V87" s="18" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="W87" s="18" t="n">
+        <v>100.83</v>
+      </c>
       <c r="X87" s="18" t="n">
-        <v>0</v>
+        <v>102.25</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" s="9" t="n"/>
-      <c r="AB87" s="5" t="n"/>
+        <v>101.9</v>
+      </c>
+      <c r="Z87" s="37" t="n">
+        <v>404.39</v>
+      </c>
+      <c r="AA87" s="18" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="AB87" s="19" t="n">
+        <v>101.03</v>
+      </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="11" t="n"/>
@@ -17137,33 +17580,79 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>2159.38</v>
       </c>
       <c r="F88" s="9" t="n"/>
+      <c r="G88" s="18" t="n">
+        <v>1303.35</v>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>-3006</v>
+      </c>
       <c r="I88" s="18" t="n">
-        <v>0</v>
+        <v>1104.56</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="K88" s="9" t="n"/>
+        <v>1005.41</v>
+      </c>
+      <c r="K88" s="37" t="n">
+        <v>407.32</v>
+      </c>
+      <c r="L88" s="18" t="n">
+        <v>1544.22</v>
+      </c>
+      <c r="M88" s="18" t="n">
+        <v>1517.11</v>
+      </c>
       <c r="N88" s="18" t="n">
-        <v>0</v>
+        <v>1178.2</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="9" t="n"/>
+        <v>316.38</v>
+      </c>
+      <c r="P88" s="37" t="n">
+        <v>4555.91</v>
+      </c>
+      <c r="Q88" s="18" t="n">
+        <v>3338.73</v>
+      </c>
+      <c r="R88" s="18" t="n">
+        <v>-9841.49</v>
+      </c>
+      <c r="S88" s="18" t="n">
+        <v>299.42</v>
+      </c>
       <c r="T88" s="18" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="U88" s="9" t="n"/>
+        <v>1877.1</v>
+      </c>
+      <c r="U88" s="37" t="n">
+        <v>-4326.24</v>
+      </c>
+      <c r="V88" s="18" t="n">
+        <v>-567.64</v>
+      </c>
+      <c r="W88" s="18" t="n">
+        <v>168.02</v>
+      </c>
+      <c r="X88" s="18" t="n">
+        <v>1902.28</v>
+      </c>
       <c r="Y88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z88" s="9" t="n"/>
-      <c r="AB88" s="5" t="n"/>
+        <v>7016.32</v>
+      </c>
+      <c r="Z88" s="37" t="n">
+        <v>8518.98</v>
+      </c>
+      <c r="AA88" s="18" t="n">
+        <v>1878.18</v>
+      </c>
+      <c r="AB88" s="19" t="n">
+        <v>3244.46</v>
+      </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -17184,56 +17673,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>2159.37</v>
       </c>
       <c r="F89" s="9" t="n"/>
+      <c r="G89" s="18" t="n">
+        <v>5159.23</v>
+      </c>
+      <c r="H89" s="18" t="n">
+        <v>-3006</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>1104.56</v>
+      </c>
       <c r="J89" s="18" t="n">
-        <v>8665.67</v>
-      </c>
-      <c r="K89" s="9" t="n"/>
+        <v>1005.42</v>
+      </c>
+      <c r="K89" s="37" t="n">
+        <v>4263.21</v>
+      </c>
+      <c r="L89" s="18" t="n">
+        <v>5807.43</v>
+      </c>
+      <c r="M89" s="18" t="n">
+        <v>1517.1</v>
+      </c>
       <c r="N89" s="18" t="n">
-        <v>1.48</v>
+        <v>1178.21</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="P89" s="9" t="n"/>
+        <v>316.38</v>
+      </c>
+      <c r="P89" s="37" t="n">
+        <v>8819.120000000001</v>
+      </c>
       <c r="Q89" s="18" t="n">
-        <v>63.57</v>
+        <v>12157.85</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>220.7</v>
+        <v>-9841.49</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>135.7</v>
+        <v>299.42</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>50.88</v>
+        <v>1877.1</v>
       </c>
       <c r="U89" s="37" t="n">
-        <v>470.85</v>
+        <v>4492.88</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>121.97</v>
+        <v>3925.24</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>58.94</v>
+        <v>168.02</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>27.35</v>
+        <v>1902.28</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>61.65</v>
+        <v>7016.32</v>
       </c>
       <c r="Z89" s="37" t="n">
-        <v>269.91</v>
+        <v>13011.86</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>46.47</v>
+        <v>14890.05</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>0</v>
+        <v>3244.46</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -17255,57 +17766,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="F90" s="9" t="n"/>
+      <c r="G90" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H90" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="J90" s="18" t="n">
-        <v>8665.67</v>
-      </c>
-      <c r="K90" s="9" t="n"/>
+        <v>2400</v>
+      </c>
+      <c r="K90" s="37" t="n">
+        <v>10400</v>
+      </c>
       <c r="N90" s="18" t="n">
-        <v>9.890000000000001</v>
+        <v>0</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>64.88</v>
+        <v>0</v>
       </c>
       <c r="P90" s="9" t="n"/>
-      <c r="Q90" s="18" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>220.7</v>
-      </c>
       <c r="S90" s="18" t="n">
-        <v>135.7</v>
+        <v>0</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="U90" s="37" t="n">
-        <v>470.85</v>
-      </c>
-      <c r="V90" s="18" t="n">
-        <v>121.97</v>
-      </c>
-      <c r="W90" s="18" t="n">
-        <v>58.94</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U90" s="9" t="n"/>
       <c r="X90" s="18" t="n">
-        <v>27.35</v>
+        <v>0</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>61.65</v>
-      </c>
-      <c r="Z90" s="37" t="n">
-        <v>269.91</v>
-      </c>
-      <c r="AA90" s="18" t="n">
-        <v>47.03</v>
-      </c>
-      <c r="AB90" s="19" t="n">
         <v>0</v>
       </c>
+      <c r="Z90" s="9" t="n"/>
+      <c r="AB90" s="5" t="n"/>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
       <c r="AE90" s="11" t="n"/>
@@ -17326,37 +17827,33 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="F91" s="9" t="n"/>
+      <c r="I91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>4.04</v>
+      </c>
       <c r="K91" s="9" t="n"/>
+      <c r="N91" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="O91" s="18" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="P91" s="9" t="n"/>
+      <c r="T91" s="18" t="n">
+        <v>4.78</v>
+      </c>
       <c r="U91" s="9" t="n"/>
-      <c r="V91" s="18" t="n">
-        <v>122.61</v>
-      </c>
-      <c r="W91" s="18" t="n">
-        <v>122.61</v>
-      </c>
-      <c r="X91" s="18" t="n">
-        <v>122.6</v>
-      </c>
       <c r="Y91" s="18" t="n">
-        <v>122.61</v>
-      </c>
-      <c r="Z91" s="37" t="n">
-        <v>490.43</v>
-      </c>
-      <c r="AA91" s="18" t="n">
-        <v>122.62</v>
-      </c>
-      <c r="AB91" s="19" t="n">
-        <v>122.63</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z91" s="9" t="n"/>
+      <c r="AB91" s="5" t="n"/>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="11" t="n"/>
@@ -17377,22 +17874,53 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="F92" s="9" t="n"/>
+      <c r="J92" s="18" t="n">
+        <v>8665.67</v>
+      </c>
       <c r="K92" s="9" t="n"/>
+      <c r="N92" s="18" t="n">
+        <v>1.48</v>
+      </c>
       <c r="O92" s="18" t="n">
-        <v>0</v>
+        <v>64.88</v>
       </c>
       <c r="P92" s="9" t="n"/>
+      <c r="Q92" s="18" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="R92" s="18" t="n">
+        <v>220.7</v>
+      </c>
+      <c r="S92" s="18" t="n">
+        <v>135.7</v>
+      </c>
       <c r="T92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" s="9" t="n"/>
-      <c r="Z92" s="9" t="n"/>
+        <v>50.88</v>
+      </c>
+      <c r="U92" s="37" t="n">
+        <v>470.85</v>
+      </c>
+      <c r="V92" s="18" t="n">
+        <v>121.97</v>
+      </c>
+      <c r="W92" s="18" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="X92" s="18" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="Y92" s="18" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="Z92" s="37" t="n">
+        <v>269.91</v>
+      </c>
       <c r="AA92" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>46.47</v>
       </c>
       <c r="AB92" s="19" t="n">
         <v>0</v>
@@ -17417,43 +17945,57 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="F93" s="9" t="n"/>
+      <c r="J93" s="18" t="n">
+        <v>8665.67</v>
+      </c>
       <c r="K93" s="9" t="n"/>
+      <c r="N93" s="18" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="O93" s="18" t="n">
+        <v>64.88</v>
+      </c>
       <c r="P93" s="9" t="n"/>
       <c r="Q93" s="18" t="n">
-        <v>8000</v>
+        <v>63.57</v>
       </c>
       <c r="R93" s="18" t="n">
+        <v>220.7</v>
+      </c>
+      <c r="S93" s="18" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="T93" s="18" t="n">
+        <v>50.88</v>
+      </c>
+      <c r="U93" s="37" t="n">
+        <v>470.85</v>
+      </c>
+      <c r="V93" s="18" t="n">
+        <v>121.97</v>
+      </c>
+      <c r="W93" s="18" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="X93" s="18" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="Y93" s="18" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="Z93" s="37" t="n">
+        <v>269.91</v>
+      </c>
+      <c r="AA93" s="18" t="n">
+        <v>47.03</v>
+      </c>
+      <c r="AB93" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="S93" s="18" t="n">
-        <v>3300</v>
-      </c>
-      <c r="T93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" s="37" t="n">
-        <v>11300</v>
-      </c>
-      <c r="V93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="5" t="n"/>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
       <c r="AE93" s="11" t="n"/>
@@ -17474,47 +18016,36 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="K94" s="9" t="n"/>
+      <c r="O94" s="18" t="n">
+        <v>0.42</v>
+      </c>
       <c r="P94" s="9" t="n"/>
-      <c r="Q94" s="18" t="n">
-        <v>8000</v>
-      </c>
-      <c r="R94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" s="18" t="n">
-        <v>4000</v>
-      </c>
-      <c r="T94" s="18" t="n">
-        <v>1100</v>
-      </c>
-      <c r="U94" s="37" t="n">
-        <v>13100</v>
-      </c>
+      <c r="U94" s="9" t="n"/>
       <c r="V94" s="18" t="n">
-        <v>800</v>
+        <v>122.61</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>700</v>
+        <v>122.61</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>0</v>
+        <v>122.6</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>0</v>
+        <v>122.61</v>
       </c>
       <c r="Z94" s="37" t="n">
-        <v>1500</v>
+        <v>490.43</v>
       </c>
       <c r="AA94" s="18" t="n">
-        <v>0</v>
+        <v>122.62</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>0</v>
+        <v>122.63</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -17536,21 +18067,26 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="K95" s="9" t="n"/>
+      <c r="O95" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P95" s="9" t="n"/>
       <c r="T95" s="18" t="n">
         <v>0</v>
       </c>
       <c r="U95" s="9" t="n"/>
-      <c r="Y95" s="18" t="n">
+      <c r="Z95" s="9" t="n"/>
+      <c r="AA95" s="18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB95" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n"/>
-      <c r="AB95" s="5" t="n"/>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
       <c r="AE95" s="11" t="n"/>
@@ -17564,6 +18100,160 @@
       <c r="AM95" s="10" t="n"/>
       <c r="AN95" s="10" t="n"/>
       <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
+      <c r="P96" s="9" t="n"/>
+      <c r="Q96" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="18" t="n">
+        <v>3300</v>
+      </c>
+      <c r="T96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="37" t="n">
+        <v>11300</v>
+      </c>
+      <c r="V96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="5" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="K97" s="9" t="n"/>
+      <c r="P97" s="9" t="n"/>
+      <c r="Q97" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>1100</v>
+      </c>
+      <c r="U97" s="37" t="n">
+        <v>13100</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>800</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AA97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
+      <c r="P98" s="9" t="n"/>
+      <c r="T98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="9" t="n"/>
+      <c r="Y98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="9" t="n"/>
+      <c r="AB98" s="5" t="n"/>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31521,7 +32211,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>447.8</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30">
@@ -31541,7 +32231,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.49</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="32">
@@ -31561,7 +32251,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1153</v>
+        <v>0.1159</v>
       </c>
     </row>
     <row r="34">
@@ -31571,7 +32261,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="35">
@@ -31591,7 +32281,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85183억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 85182억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 88314억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91228억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 91241억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94600억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94620억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99289억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99317억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105070억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 105097억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111421억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 111447억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117844억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 117868억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123670억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 123693억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85183억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85182억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88314억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91228억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91241억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94600억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94620억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99289억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99317억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105070억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105097억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111421억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111447억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117844억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117868억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123670억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123693억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -4422,7 +4422,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 21.99% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -6.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 4.1% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -6.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 4.1% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
     </row>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2905</v>
+        <v>2880</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3023</v>
+        <v>3018</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6565,29 +6565,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.078226906</v>
+        <v>0.078335642</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.028941372</v>
+        <v>-0.028855612</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179173188</v>
+        <v>0.179449406</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165612648</v>
+        <v>0.165942029</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189895119</v>
+        <v>0.190077644</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221319438</v>
+        <v>0.22147651</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245724994</v>
+        <v>0.245745511</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245563468</v>
+        <v>0.245437595</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6879,32 +6879,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.178398548</v>
+        <v>0.178380559</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178397951</v>
+        <v>0.178382197</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178418053</v>
+        <v>0.178376269</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178365548</v>
+        <v>0.178371659</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.17840495</v>
+        <v>0.1783596</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178393232</v>
+        <v>0.17835454</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.178387865</v>
+        <v>0.178343151</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178365625</v>
+        <v>0.178378624</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.000594952</v>
+        <v>-0.001602013</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.00538313</v>
+        <v>0.002263797</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.004933406</v>
+        <v>-0.006932139</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.006114923</v>
+        <v>0.003815266</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.006772416</v>
+        <v>-0.005842963</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.005085886</v>
+        <v>-0.000772126</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.001805738</v>
+        <v>-0.000595518</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.000728797</v>
+        <v>-0.003565817</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.009922965000000001</v>
+        <v>-0.003366139</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.001516197</v>
+        <v>0.001698157</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.000594952</v>
+        <v>-0.001602013</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.00538313</v>
+        <v>0.002263797</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.004933406</v>
+        <v>-0.006932139</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.006114923</v>
+        <v>0.003815266</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.006772416</v>
+        <v>-0.005842963</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.005085886</v>
+        <v>-0.000772126</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.001805738</v>
+        <v>-0.000595518</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.000728797</v>
+        <v>-0.003565817</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.009922965000000001</v>
+        <v>-0.003366139</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.001516197</v>
+        <v>0.001698157</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8326,23 +8326,23 @@
         <v>0.139373107</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.137192932</v>
+        <v>0.137264761</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.163592724</v>
+        <v>0.163582391</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.09608077299999999</v>
+        <v>0.096129838</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.101723455</v>
+        <v>0.10171338</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.105592017</v>
+        <v>0.105627472</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.129945111</v>
+        <v>0.129969916</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8451,26 +8451,26 @@
         <v>0.068360172</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.07230808399999999</v>
+        <v>0.072350543</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.075628588</v>
+        <v>0.075625594</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.09534327300000001</v>
+        <v>0.09537657400000001</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.059519409</v>
+        <v>0.059481803</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.06512085300000001</v>
+        <v>0.065150506</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.06995443599999999</v>
+        <v>0.069980048</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.08898352299999999</v>
+        <v>0.08897609300000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9133,11 +9133,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2905</v>
+        <v>2880</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,075원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,950원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2199282976882185</v>
+        <v>0.2200477916941332</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1138951358538069</v>
+        <v>0.1138970203498649</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001044049219686043</v>
+        <v>0.001043874528198475</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03627019823816484</v>
+        <v>0.03626987818853011</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.46</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="32">
@@ -32241,7 +32241,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="33">
@@ -32281,7 +32281,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85182억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 85181억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88314억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 88310억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91241억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 91234억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94620억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94611억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99317억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99305억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105097억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 105085억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111447억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 111436억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117868억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 117858억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123693억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 123684억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85182억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85181억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88314억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88310억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91241억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91234억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94620억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94611억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99317억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99305억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105097억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105085억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111447억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111436억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117868억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117858억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123693억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123684억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6568,26 +6568,26 @@
         <v>0.078335642</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.028855612</v>
+        <v>-0.028941372</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179449406</v>
+        <v>0.179357334</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165942029</v>
+        <v>0.165810277</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.190077644</v>
+        <v>0.189976808</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.22147651</v>
+        <v>0.22149607</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245745511</v>
+        <v>0.245686627</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245437595</v>
+        <v>0.245465333</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6882,29 +6882,29 @@
         <v>0.178380559</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178382197</v>
+        <v>0.178397951</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178376269</v>
+        <v>0.178390194</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178371659</v>
+        <v>0.178391818</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.1783596</v>
+        <v>0.178374714</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.17835454</v>
+        <v>0.178367435</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.178343151</v>
+        <v>0.178365505</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178378624</v>
+        <v>0.17839481</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.001602013</v>
+        <v>-0.000586605</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.002263797</v>
+        <v>0.003705301</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.006932139</v>
+        <v>-0.006008444</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.003815266</v>
+        <v>0.004877936</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.005842963</v>
+        <v>0.005364353</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.000772126</v>
+        <v>0.000917285</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.000595518</v>
+        <v>0.000513721</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.003565817</v>
+        <v>-0.002254262</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.003366139</v>
+        <v>-0.001846823</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.001698157</v>
+        <v>0.003817691</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.001602013</v>
+        <v>-0.000586605</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002263797</v>
+        <v>0.003705301</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.006932139</v>
+        <v>-0.006008444</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.003815266</v>
+        <v>0.004877936</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.005842963</v>
+        <v>0.005364353</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.000772126</v>
+        <v>0.000917285</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.000595518</v>
+        <v>0.000513721</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.003565817</v>
+        <v>-0.002254262</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.003366139</v>
+        <v>-0.001846823</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.001698157</v>
+        <v>0.003817691</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8326,23 +8326,23 @@
         <v>0.139373107</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.137264761</v>
+        <v>0.137192932</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.163582391</v>
+        <v>0.163655887</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.096129838</v>
+        <v>0.09607555800000001</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.10171338</v>
+        <v>0.101718417</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.105627472</v>
+        <v>0.10563222</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.129969916</v>
+        <v>0.129934545</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8451,26 +8451,26 @@
         <v>0.068360172</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.072350543</v>
+        <v>0.07230808399999999</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.075625594</v>
+        <v>0.075628588</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.09537657400000001</v>
+        <v>0.095380085</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.059481803</v>
+        <v>0.059517408</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.065150506</v>
+        <v>0.065118787</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.069980048</v>
+        <v>0.069982132</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.08897609300000001</v>
+        <v>0.088950738</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2200477916941332</v>
+        <v>0.219992583130743</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1138970203498649</v>
+        <v>0.1138909317191831</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001043874528198475</v>
+        <v>0.001043937764966655</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03626987818853011</v>
+        <v>0.0362699812974335</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2880</v>
+        <v>2830</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6315,7 +6315,7 @@
         <v>2475</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2870</v>
+        <v>2780</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3018</v>
+        <v>2986.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2880</v>
+        <v>2830</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30091,7 +30091,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.4</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="32">
@@ -32241,7 +32241,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="33">
@@ -32281,7 +32281,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85181억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 85179억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88310억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 88295억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91234억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 91206억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94611억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94568억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99305억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99251억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105085억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 105030억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111436억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 111381억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117858억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 117805억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123684억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 123634억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85181억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85179억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88310억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88295억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91234억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91206억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94611억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94568억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99305억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99251억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105085억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105030억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111436억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111381억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117858억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117805억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123684억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123634억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2830</v>
+        <v>2755</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6315,7 +6315,7 @@
         <v>2475</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2780</v>
+        <v>2595</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2986.7</v>
+        <v>2952.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6561,33 +6561,33 @@
         <v>-0.056111852</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.164585552</v>
+        <v>0.164508833</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.078335642</v>
+        <v>0.07811817</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.028941372</v>
+        <v>-0.029198652</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179357334</v>
+        <v>0.178804898</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165810277</v>
+        <v>0.165228276</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189976808</v>
+        <v>0.189510842</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.22149607</v>
+        <v>0.221201413</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245686627</v>
+        <v>0.245723659</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245465333</v>
+        <v>0.245660655</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6872,39 +6872,39 @@
         <v>0.178344535</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.178392622</v>
+        <v>0.178404374</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.178380559</v>
+        <v>0.178416541</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178397951</v>
+        <v>0.17835689</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178390194</v>
+        <v>0.178395689</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178391818</v>
+        <v>0.178379601</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.178374714</v>
+        <v>0.178395794</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178367435</v>
+        <v>0.178385417</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.178365505</v>
+        <v>0.17838109</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.17839481</v>
+        <v>0.178376906</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.000586605</v>
+        <v>-0.000240562</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.003705301</v>
+        <v>0.004198808</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.006008444</v>
+        <v>0.00430894</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.004877936</v>
+        <v>-0.002556155</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.005364353</v>
+        <v>-0.002017966</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.000917285</v>
+        <v>0.005899488</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.000513721</v>
+        <v>0.00309474</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.002254262</v>
+        <v>0.000394939</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.001846823</v>
+        <v>0.00087387</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.003817691</v>
+        <v>-0.001056219</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.000586605</v>
+        <v>-0.000240562</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.003705301</v>
+        <v>0.004198808</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.006008444</v>
+        <v>0.00430894</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.004877936</v>
+        <v>-0.002556155</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.005364353</v>
+        <v>-0.002017966</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.000917285</v>
+        <v>0.005899488</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.000513721</v>
+        <v>0.00309474</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.002254262</v>
+        <v>0.000394939</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.001846823</v>
+        <v>0.00087387</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.003817691</v>
+        <v>-0.001056219</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8323,26 +8323,26 @@
         <v>0.140683346</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.139373107</v>
+        <v>0.139291268</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.137192932</v>
+        <v>0.137202787</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.163655887</v>
+        <v>0.16353989</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.09607555800000001</v>
+        <v>0.096091205</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.101718417</v>
+        <v>0.101634473</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.10563222</v>
+        <v>0.105611006</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.129934545</v>
+        <v>0.129925583</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8454,23 +8454,23 @@
         <v>0.07230808399999999</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.075628588</v>
+        <v>0.07558899199999999</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.095380085</v>
+        <v>0.09530996899999999</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.059517408</v>
+        <v>0.059489799</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.065118787</v>
+        <v>0.06509532699999999</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.069982132</v>
+        <v>0.06996276999999999</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.088950738</v>
+        <v>0.08893775700000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9133,11 +9133,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2830</v>
+        <v>2755</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,950원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,905원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.219992583130743</v>
+        <v>0.2199736213007996</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1138909317191831</v>
+        <v>0.1138762344019694</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001043937764966655</v>
+        <v>0.001044334728113209</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0362699812974335</v>
+        <v>0.03627074290641113</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30091,7 +30091,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32211,7 +32211,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>450</v>
+        <v>449.9</v>
       </c>
     </row>
     <row r="30">
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="32">
@@ -32241,7 +32241,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="33">
@@ -32251,7 +32251,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1159</v>
+        <v>0.1158</v>
       </c>
     </row>
     <row r="34">
@@ -32281,7 +32281,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.47</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88295억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91206억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 91230억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94568억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94604억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99251억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99299억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105030억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 105077억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111381억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 111427억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117805억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 117848억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123634억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 123674억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1656,49 +1656,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88295억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91206억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91230억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94568억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94604억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99251억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99299억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105030억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105077억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111381억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111427억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117805억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117848억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123634억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123674억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2755</v>
+        <v>2810</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2952.1</v>
+        <v>2938.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6565,29 +6565,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.07811817</v>
+        <v>0.078226906</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.029198652</v>
+        <v>-0.028941372</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.178804898</v>
+        <v>0.179265261</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165228276</v>
+        <v>0.1658212</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189510842</v>
+        <v>0.189995966</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221201413</v>
+        <v>0.221407754</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245723659</v>
+        <v>0.245705809</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245660655</v>
+        <v>0.245479204</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6879,32 +6879,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.178416541</v>
+        <v>0.178398548</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.17835689</v>
+        <v>0.178397951</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178395689</v>
+        <v>0.178404122</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178379601</v>
+        <v>0.178345389</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.178395794</v>
+        <v>0.178389831</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178385417</v>
+        <v>0.178380333</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.17838109</v>
+        <v>0.178376684</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178376906</v>
+        <v>0.178357532</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.000240562</v>
+        <v>4.041e-06</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.004198808</v>
+        <v>0.004544031</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.00430894</v>
+        <v>-0.005470966</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.002556155</v>
+        <v>0.005496429</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.002017966</v>
+        <v>0.00606838</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.005899488</v>
+        <v>-0.005898406</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.00309474</v>
+        <v>0.01116092</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.000394939</v>
+        <v>-0.001492311</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.00087387</v>
+        <v>-0.000962747</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.001056219</v>
+        <v>-0.002749069</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.000240562</v>
+        <v>4.041e-06</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.004198808</v>
+        <v>0.004544031</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.00430894</v>
+        <v>-0.005470966</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>-0.002556155</v>
+        <v>0.005496429</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.002017966</v>
+        <v>0.00606838</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.005899488</v>
+        <v>-0.005898406</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.00309474</v>
+        <v>0.01116092</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.000394939</v>
+        <v>-0.001492311</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.00087387</v>
+        <v>-0.000962747</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.001056219</v>
+        <v>-0.002749069</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8323,26 +8323,26 @@
         <v>0.140683346</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.139291268</v>
+        <v>0.139373107</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.137202787</v>
+        <v>0.137192932</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.16353989</v>
+        <v>0.163592724</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.096091205</v>
+        <v>0.096135056</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.101634473</v>
+        <v>0.101668895</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.105611006</v>
+        <v>0.105636968</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.129925583</v>
+        <v>0.129939828</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8454,23 +8454,23 @@
         <v>0.07230808399999999</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.07558899199999999</v>
+        <v>0.075628588</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.09530996899999999</v>
+        <v>0.095380085</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.059489799</v>
+        <v>0.059483802</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.06509532699999999</v>
+        <v>0.06512085300000001</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.06996276999999999</v>
+        <v>0.069984216</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.08893775700000001</v>
+        <v>0.088953213</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9133,11 +9133,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2755</v>
+        <v>2810</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,905원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,800원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2199736213007996</v>
+        <v>0.2199604417339707</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1138762344019694</v>
+        <v>0.1138903032360262</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001044334728113209</v>
+        <v>0.001044006183494015</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03627074290641113</v>
+        <v>0.03627011511230561</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30091,7 +30091,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32211,7 +32211,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>449.9</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30">
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.12</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="32">
@@ -32241,7 +32241,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="33">
@@ -32251,7 +32251,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1158</v>
+        <v>0.1159</v>
       </c>
     </row>
     <row r="34">
@@ -32281,7 +32281,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85179억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 85298억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 88507억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91230억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 91437억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94604억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94759억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99299억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99239억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105077억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 104812억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111427억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 111021억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117848억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 117367억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123674억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 123182억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85179억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85298억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88507억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91230억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91437억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94604억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94759억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99299억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99239억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105077억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 104812억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111427억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111021억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117848억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117367억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123674억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123182억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2810</v>
+        <v>2725</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6315,7 +6315,7 @@
         <v>2475</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2595</v>
+        <v>2585</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2938.8</v>
+        <v>2876.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6561,33 +6561,33 @@
         <v>-0.056111852</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.164508833</v>
+        <v>0.166196639</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.078226906</v>
+        <v>0.080727836</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.028941372</v>
+        <v>-0.026711616</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179265261</v>
+        <v>0.181198785</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.1658212</v>
+        <v>0.163410302</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189995966</v>
+        <v>0.184223765</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221407754</v>
+        <v>0.214115781</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245705809</v>
+        <v>0.238600047</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245479204</v>
+        <v>0.241277919</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6872,39 +6872,39 @@
         <v>0.178344535</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.178404374</v>
+        <v>0.17834353</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.178398548</v>
+        <v>0.178388168</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178397951</v>
+        <v>0.178341704</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178404122</v>
+        <v>0.178345935</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178345389</v>
+        <v>0.178399774</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.178389831</v>
+        <v>0.178334749</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178380333</v>
+        <v>0.178387401</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.178376684</v>
+        <v>0.178351164</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178357532</v>
+        <v>0.178389213</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>4.041e-06</v>
+        <v>-0.000553264</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.004544031</v>
+        <v>-0.002841034</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.005470966</v>
+        <v>-0.004770662</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.005496429</v>
+        <v>0.006128894</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.00606838</v>
+        <v>-0.011169092</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.005898406</v>
+        <v>0.005412113</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.01116092</v>
+        <v>0.003779339</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.001492311</v>
+        <v>-0.002389091</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.000962747</v>
+        <v>-0.005385727</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.002749069</v>
+        <v>0.009088308</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>4.041e-06</v>
+        <v>-0.000553264</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.004544031</v>
+        <v>-0.002841034</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.005470966</v>
+        <v>-0.004770662</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.005496429</v>
+        <v>0.006128894</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.00606838</v>
+        <v>-0.011169092</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.005898406</v>
+        <v>0.005412113</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.01116092</v>
+        <v>0.003779339</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.001492311</v>
+        <v>-0.002389091</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.000962747</v>
+        <v>-0.005385727</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.002749069</v>
+        <v>0.009088308</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8316,33 +8316,33 @@
         <v>0.239520108</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.264251151</v>
+        <v>0.264605217</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.140683346</v>
+        <v>0.140923938</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.139373107</v>
+        <v>0.139631902</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.137192932</v>
+        <v>0.13730979</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.163592724</v>
+        <v>0.163332281</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.096135056</v>
+        <v>0.095860685</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.101668895</v>
+        <v>0.101287129</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.105636968</v>
+        <v>0.105187449</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.129939828</v>
+        <v>0.12954527</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8444,33 +8444,33 @@
         <v>0.090158958</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.112990357</v>
+        <v>0.113141819</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.068360172</v>
+        <v>0.068486938</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.07230808399999999</v>
+        <v>0.072459462</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.075628588</v>
+        <v>0.07571739600000001</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.095380085</v>
+        <v>0.095260873</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.059483802</v>
+        <v>0.059327443</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.06512085300000001</v>
+        <v>0.06488440700000001</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.069984216</v>
+        <v>0.069716192</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.088953213</v>
+        <v>0.088641425</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9133,11 +9133,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2810</v>
+        <v>2725</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,800원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,605원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2199604417339707</v>
+        <v>0.2199900998267469</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1138903032360262</v>
+        <v>0.1138933135110261</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.001044006183494015</v>
+        <v>0.00104421477434002</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03627011511230561</v>
+        <v>0.03627098645105468</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30091,7 +30091,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32211,7 +32211,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>450</v>
+        <v>450.6</v>
       </c>
     </row>
     <row r="30">
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.24</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="32">
@@ -32241,7 +32241,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33">
@@ -32251,7 +32251,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1159</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="34">
@@ -32281,7 +32281,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/099410_model.xlsx
+++ b/argus/kship/models/099410_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85298억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 85391억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88507억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 88678억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91437억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 91629억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94759억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 94927억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99239억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 99258억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 104812억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 104675억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111021억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 110775억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117367억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 117063억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123182억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−0) 122870억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85298억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85391억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88507억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88678억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91437억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91629억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94759억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94927억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99239억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99258억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 104812억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 104675억 × 비례계수 0.0055 × 계절비중 Q1 0.204(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111021억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 110775억 × 비례계수 0.0055 × 계절비중 Q2 0.226(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117367억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117063억 × 비례계수 0.0055 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123182억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−0) 122870억 × 비례계수 0.0055 × 계절비중 Q4 0.324(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2016,7 +2016,7 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 220억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 221억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2076,7 +2076,7 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 221억 × 0.10%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 113억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4294,7 +4294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5165,35 +5165,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5284,35 +5284,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5403,35 +5403,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5522,35 +5522,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5641,35 +5641,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5760,35 +5760,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5879,35 +5879,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5998,35 +5998,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6133,7 +6133,7 @@
         <v>3100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2725</v>
+        <v>2450</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6315,7 +6315,7 @@
         <v>2475</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2585</v>
+        <v>2450</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
         <v>3134.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2876.4</v>
+        <v>2785.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6561,33 +6561,33 @@
         <v>-0.056111852</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.166196639</v>
+        <v>0.167424133</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.080727836</v>
+        <v>0.082793821</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.026711616</v>
+        <v>-0.02473914</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.181198785</v>
+        <v>0.183316453</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.163410302</v>
+        <v>0.162384176</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.184223765</v>
+        <v>0.180357502</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.214115781</v>
+        <v>0.20902216</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.238600047</v>
+        <v>0.233193277</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.241277919</v>
+        <v>0.237901402</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6872,39 +6872,39 @@
         <v>0.178344535</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.17834353</v>
+        <v>0.178353158</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.178388168</v>
+        <v>0.178349066</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.178341704</v>
+        <v>0.178420682</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.178345935</v>
+        <v>0.178338002</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.178399774</v>
+        <v>0.178369516</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.178334749</v>
+        <v>0.178407351</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.178387401</v>
+        <v>0.178340243</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.178351164</v>
+        <v>0.178370875</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.178389213</v>
+        <v>0.178388747</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7929,36 +7929,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.000553264</v>
+        <v>-0.000711343</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.002841034</v>
+        <v>-0.009663847999999999</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.004770662</v>
+        <v>-0.001511372</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.006128894</v>
+        <v>0.004970687</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.011169092</v>
+        <v>-0.000143967</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.005412113</v>
+        <v>-0.004829414</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.003779339</v>
+        <v>0.008025498000000001</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.002389091</v>
+        <v>-0.009377767</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.005385727</v>
+        <v>-0.000214821</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.009088308</v>
+        <v>0.010756314</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8057,36 +8057,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.000553264</v>
+        <v>-0.000711343</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.002841034</v>
+        <v>-0.009663847999999999</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.004770662</v>
+        <v>-0.001511372</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.006128894</v>
+        <v>0.004970687</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.011169092</v>
+        <v>-0.000143967</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.005412113</v>
+        <v>-0.004829414</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.003779339</v>
+        <v>0.008025498000000001</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.002389091</v>
+        <v>-0.009377767</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.005385727</v>
+        <v>-0.000214821</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.009088308</v>
+        <v>0.010756314</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8316,33 +8316,33 @@
         <v>0.239520108</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.264605217</v>
+        <v>0.26484126</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.140923938</v>
+        <v>0.141177568</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.139631902</v>
+        <v>0.139820114</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.13730979</v>
+        <v>0.137446198</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.163332281</v>
+        <v>0.163282038</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.095860685</v>
+        <v>0.095689889</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.101287129</v>
+        <v>0.10103909</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.105187449</v>
+        <v>0.104889448</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.12954527</v>
+        <v>0.129219881</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8444,33 +8444,33 @@
         <v>0.090158958</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.113141819</v>
+        <v>0.11329328</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.068486938</v>
+        <v>0.068568319</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.072459462</v>
+        <v>0.07257140400000001</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.07571739600000001</v>
+        <v>0.075812132</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.095260873</v>
+        <v>0.09525911200000001</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.059327443</v>
+        <v>0.059236375</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.06488440700000001</v>
+        <v>0.064737026</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.069716192</v>
+        <v>0.069525086</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.088641425</v>
+        <v>0.088418708</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9133,11 +9133,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2725</v>
+        <v>2450</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,605원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,625원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2199900998267469</v>
+        <v>0.2199983492901948</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1138933135110261</v>
+        <v>0.1138984107198504</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.00104421477434002</v>
+        <v>0.001043922720547599</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03627098645105468</v>
+        <v>0.0362708049361416</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30091,7 +30091,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32211,7 +32211,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>450.6</v>
+        <v>451.3</v>
       </c>
     </row>
     <row r="30">
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.05</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="32">
@@ -32241,7 +32241,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="33">
@@ -32251,7 +32251,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.116</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="34">
@@ -32281,7 +32281,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.31</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="37">
